--- a/注塑项目/金榕/GEA轮罩 /GEA轮罩技术协议和产品特殊特性清单 （新）202260717/轮罩件特殊特性.xlsx
+++ b/注塑项目/金榕/GEA轮罩 /GEA轮罩技术协议和产品特殊特性清单 （新）202260717/轮罩件特殊特性.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chensiyuan5/Desktop/Github/shenyuan_work/注塑项目/金榕/GEA轮罩 /GEA轮罩技术协议和产品特殊特性清单 （新）202260717/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9640E6E-3933-0A4D-B254-0D5867EA677A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A1EA82-7841-9D44-95B6-EDB379F5CB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="7560" windowWidth="23220" windowHeight="11200" tabRatio="916" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="2360" windowWidth="23560" windowHeight="14980" tabRatio="916" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="成品 特性" sheetId="54" r:id="rId1"/>
@@ -359,9 +359,6 @@
     <t>结构缓冲性能</t>
   </si>
   <si>
-    <t>实验由金榕完成</t>
-  </si>
-  <si>
     <t>过程特殊特性清单</t>
   </si>
   <si>
@@ -2724,6 +2721,9 @@
   </si>
   <si>
     <t>深远提供样件，由金榕完成实验</t>
+  </si>
+  <si>
+    <t>深远提供样件，实验由金榕完成</t>
   </si>
 </sst>
 </file>
@@ -3704,7 +3704,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="303">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4064,8 +4064,14 @@
     <xf numFmtId="0" fontId="27" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4077,12 +4083,84 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4110,12 +4188,6 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="15" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -4125,80 +4197,197 @@
     <xf numFmtId="14" fontId="13" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4208,13 +4397,219 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4232,404 +4627,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4889,14 +4886,11 @@
               <a:pPr algn="ctr"/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" altLang="zh-CN" sz="1200" i="1">
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="1">
                             <a:solidFill>
                               <a:srgbClr val="0070C0"/>
                             </a:solidFill>
@@ -4961,7 +4955,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="">
+      <mc:Fallback xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
         <xdr:sp>
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="文本框 48"/>
@@ -5314,14 +5308,11 @@
               <a:pPr algn="ctr"/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" altLang="zh-CN" sz="1200" i="1">
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="1">
                             <a:solidFill>
                               <a:srgbClr val="0070C0"/>
                             </a:solidFill>
@@ -5386,7 +5377,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="">
+      <mc:Fallback xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
         <xdr:sp>
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="文本框 30"/>
@@ -8816,17 +8807,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="78" customHeight="1">
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="2:11" ht="20" customHeight="1">
       <c r="B3" s="92" t="s">
@@ -8841,11 +8832,11 @@
       <c r="E3" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126" t="s">
+      <c r="F3" s="128"/>
+      <c r="G3" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="126"/>
+      <c r="H3" s="128"/>
       <c r="I3" s="92" t="s">
         <v>6</v>
       </c>
@@ -8866,9 +8857,9 @@
       <c r="E4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
       <c r="I4" s="97" t="s">
         <v>12</v>
       </c>
@@ -8889,9 +8880,9 @@
       <c r="E5" s="96">
         <v>2026.6</v>
       </c>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
       <c r="I5" s="97" t="s">
         <v>16</v>
       </c>
@@ -8904,9 +8895,9 @@
       <c r="C6" s="100"/>
       <c r="D6" s="101"/>
       <c r="E6" s="102"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
       <c r="I6" s="103" t="s">
         <v>18</v>
       </c>
@@ -8983,7 +8974,7 @@
         <v>36</v>
       </c>
       <c r="K9" s="122" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="2:11" s="89" customFormat="1" ht="27" customHeight="1">
@@ -9035,7 +9026,7 @@
       <c r="G11" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="299" t="s">
+      <c r="H11" s="110" t="s">
         <v>34</v>
       </c>
       <c r="I11" s="110" t="s">
@@ -9074,8 +9065,8 @@
       <c r="J12" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="298" t="s">
-        <v>305</v>
+      <c r="K12" s="124" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="2:11" s="90" customFormat="1" ht="80">
@@ -9097,7 +9088,7 @@
       <c r="G13" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="299" t="s">
+      <c r="H13" s="110" t="s">
         <v>34</v>
       </c>
       <c r="I13" s="110" t="s">
@@ -9136,8 +9127,8 @@
       <c r="J14" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="300" t="s">
-        <v>305</v>
+      <c r="K14" s="133" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="2:11" s="90" customFormat="1" ht="34">
@@ -9166,7 +9157,7 @@
         <v>53</v>
       </c>
       <c r="J15" s="113"/>
-      <c r="K15" s="300"/>
+      <c r="K15" s="133"/>
     </row>
     <row r="16" spans="2:11" s="90" customFormat="1" ht="85">
       <c r="B16" s="110">
@@ -9194,7 +9185,7 @@
         <v>53</v>
       </c>
       <c r="J16" s="113"/>
-      <c r="K16" s="300"/>
+      <c r="K16" s="133"/>
     </row>
     <row r="17" spans="2:10" s="90" customFormat="1">
       <c r="B17" s="113"/>
@@ -9241,29 +9232,29 @@
       <c r="J20" s="113"/>
     </row>
     <row r="21" spans="2:10" s="90" customFormat="1">
-      <c r="B21" s="127" t="s">
+      <c r="B21" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="127"/>
-      <c r="D21" s="127"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="127"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="129"/>
     </row>
     <row r="22" spans="2:10" s="90" customFormat="1" ht="17">
       <c r="B22" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="124" t="s">
+      <c r="C22" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="124"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="124"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="130"/>
       <c r="H22" s="92" t="s">
         <v>72</v>
       </c>
@@ -9276,12 +9267,12 @@
     </row>
     <row r="23" spans="2:10">
       <c r="B23" s="112"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="131"/>
       <c r="I23" s="96"/>
       <c r="J23" s="96"/>
     </row>
@@ -9327,17 +9318,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="78" customHeight="1">
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="127" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="2:11" ht="20" customHeight="1">
       <c r="B3" s="92" t="s">
@@ -9352,11 +9343,11 @@
       <c r="E3" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126" t="s">
+      <c r="F3" s="128"/>
+      <c r="G3" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="126"/>
+      <c r="H3" s="128"/>
       <c r="I3" s="92" t="s">
         <v>6</v>
       </c>
@@ -9377,9 +9368,9 @@
       <c r="E4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
       <c r="I4" s="97" t="s">
         <v>12</v>
       </c>
@@ -9400,9 +9391,9 @@
       <c r="E5" s="96">
         <v>2026.6</v>
       </c>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
       <c r="I5" s="97" t="s">
         <v>16</v>
       </c>
@@ -9415,9 +9406,9 @@
       <c r="C6" s="100"/>
       <c r="D6" s="101"/>
       <c r="E6" s="102"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
       <c r="I6" s="103" t="s">
         <v>18</v>
       </c>
@@ -9493,8 +9484,8 @@
       <c r="J9" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="301" t="s">
-        <v>82</v>
+      <c r="K9" s="134" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="2:11" s="89" customFormat="1" ht="160">
@@ -9525,7 +9516,7 @@
       <c r="J10" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="K10" s="301"/>
+      <c r="K10" s="134"/>
     </row>
     <row r="11" spans="2:11" s="89" customFormat="1" ht="32">
       <c r="B11" s="110">
@@ -9553,7 +9544,7 @@
         <v>35</v>
       </c>
       <c r="J11" s="110"/>
-      <c r="K11" s="301"/>
+      <c r="K11" s="134"/>
     </row>
     <row r="12" spans="2:11" s="89" customFormat="1">
       <c r="B12" s="112"/>
@@ -9611,29 +9602,29 @@
       <c r="J16" s="117"/>
     </row>
     <row r="17" spans="2:10" s="90" customFormat="1">
-      <c r="B17" s="127" t="s">
+      <c r="B17" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="127"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="129"/>
     </row>
     <row r="18" spans="2:10" s="90" customFormat="1" ht="17">
       <c r="B18" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="124" t="s">
+      <c r="C18" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="124"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
       <c r="H18" s="92" t="s">
         <v>72</v>
       </c>
@@ -9646,25 +9637,25 @@
     </row>
     <row r="19" spans="2:10">
       <c r="B19" s="112"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
+      <c r="C19" s="131"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="131"/>
       <c r="I19" s="96"/>
       <c r="J19" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="G4:H6"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="F3:F6"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="G4:H6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D1048576" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -9697,17 +9688,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="78" customHeight="1">
-      <c r="B2" s="125" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
+      <c r="B2" s="127" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="2:15" ht="20" customHeight="1">
       <c r="B3" s="92" t="s">
@@ -9722,11 +9713,11 @@
       <c r="E3" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126" t="s">
+      <c r="F3" s="128"/>
+      <c r="G3" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="126"/>
+      <c r="H3" s="128"/>
       <c r="I3" s="92" t="s">
         <v>6</v>
       </c>
@@ -9747,9 +9738,9 @@
       <c r="E4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
       <c r="I4" s="97" t="s">
         <v>12</v>
       </c>
@@ -9770,14 +9761,14 @@
       <c r="E5" s="96">
         <v>2026.6</v>
       </c>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
       <c r="I5" s="97" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="98" t="s">
         <v>84</v>
-      </c>
-      <c r="J5" s="98" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="17">
@@ -9785,9 +9776,9 @@
       <c r="C6" s="100"/>
       <c r="D6" s="101"/>
       <c r="E6" s="102"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
       <c r="I6" s="103" t="s">
         <v>18</v>
       </c>
@@ -9840,31 +9831,31 @@
         <v>1</v>
       </c>
       <c r="C9" s="110" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" s="110" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="110" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="110" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="110" t="s">
+      <c r="G9" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="111" t="s">
+      <c r="H9" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="H9" s="110" t="s">
+      <c r="I9" s="110" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="110" t="s">
+      <c r="J9" s="110" t="s">
         <v>91</v>
       </c>
-      <c r="J9" s="110" t="s">
+      <c r="O9" s="110" t="s">
         <v>92</v>
-      </c>
-      <c r="O9" s="110" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="10" spans="2:15" s="89" customFormat="1" ht="68">
@@ -9872,13 +9863,13 @@
         <v>2</v>
       </c>
       <c r="C10" s="110" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="110" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="110" t="s">
+      <c r="E10" s="110" t="s">
         <v>95</v>
-      </c>
-      <c r="E10" s="110" t="s">
-        <v>96</v>
       </c>
       <c r="F10" s="110" t="s">
         <v>32</v>
@@ -9887,19 +9878,19 @@
         <v>33</v>
       </c>
       <c r="H10" s="119" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I10" s="110" t="s">
         <v>35</v>
       </c>
       <c r="J10" s="110" t="s">
+        <v>97</v>
+      </c>
+      <c r="K10" s="125" t="s">
+        <v>302</v>
+      </c>
+      <c r="O10" s="110" t="s">
         <v>98</v>
-      </c>
-      <c r="K10" s="302" t="s">
-        <v>303</v>
-      </c>
-      <c r="O10" s="110" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="11" spans="2:15" s="89" customFormat="1" ht="32" customHeight="1">
@@ -9907,32 +9898,32 @@
         <v>3</v>
       </c>
       <c r="C11" s="110" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D11" s="110" t="s">
         <v>38</v>
       </c>
       <c r="E11" s="110" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="110" t="s">
         <v>101</v>
-      </c>
-      <c r="F11" s="110" t="s">
-        <v>102</v>
       </c>
       <c r="G11" s="111" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="110" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I11" s="110" t="s">
         <v>46</v>
       </c>
       <c r="J11" s="110" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K11" s="111"/>
       <c r="O11" s="110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="2:15" s="89" customFormat="1" ht="34">
@@ -9940,13 +9931,13 @@
         <v>4</v>
       </c>
       <c r="C12" s="110" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" s="110" t="s">
         <v>38</v>
       </c>
       <c r="E12" s="110" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F12" s="110" t="s">
         <v>61</v>
@@ -9955,7 +9946,7 @@
         <v>33</v>
       </c>
       <c r="H12" s="119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I12" s="110" t="s">
         <v>35</v>
@@ -9963,11 +9954,11 @@
       <c r="J12" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="K12" s="303" t="s">
+      <c r="K12" s="126" t="s">
         <v>66</v>
       </c>
       <c r="O12" s="110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="2:15" s="89" customFormat="1" ht="27" customHeight="1">
@@ -9975,13 +9966,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="110" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" s="110" t="s">
         <v>38</v>
       </c>
       <c r="E13" s="110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F13" s="110" t="s">
         <v>57</v>
@@ -9996,11 +9987,11 @@
         <v>35</v>
       </c>
       <c r="J13" s="110" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K13" s="111"/>
       <c r="O13" s="110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="2:15" s="89" customFormat="1">
@@ -10048,29 +10039,29 @@
       <c r="J17" s="113"/>
     </row>
     <row r="18" spans="2:10" s="90" customFormat="1">
-      <c r="B18" s="127" t="s">
+      <c r="B18" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="127"/>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
+      <c r="C18" s="129"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="129"/>
     </row>
     <row r="19" spans="2:10" s="90" customFormat="1" ht="17">
       <c r="B19" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="124" t="s">
+      <c r="C19" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="124"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="124"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
       <c r="H19" s="92" t="s">
         <v>72</v>
       </c>
@@ -10083,12 +10074,12 @@
     </row>
     <row r="20" spans="2:10">
       <c r="B20" s="112"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="128"/>
+      <c r="C20" s="131"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="131"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="131"/>
       <c r="I20" s="96"/>
       <c r="J20" s="96"/>
     </row>
@@ -10138,113 +10129,113 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1"/>
     <row r="2" spans="2:14" ht="30" customHeight="1">
-      <c r="B2" s="130" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="132"/>
+      <c r="B2" s="156" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="158"/>
     </row>
     <row r="3" spans="2:14" ht="43">
       <c r="B3" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="D3" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="E3" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="F3" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="G3" s="159" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="133" t="s">
+      <c r="H3" s="160"/>
+      <c r="I3" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="134"/>
-      <c r="I3" s="30" t="s">
+      <c r="J3" s="161"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="J3" s="135"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="M3" s="137"/>
-      <c r="N3" s="138"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="164"/>
     </row>
     <row r="4" spans="2:14" ht="58">
       <c r="B4" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="E4" s="159" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="160"/>
+      <c r="G4" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="133" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="134"/>
-      <c r="G4" s="139" t="s">
+      <c r="H4" s="143"/>
+      <c r="I4" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="H4" s="140"/>
-      <c r="I4" s="30" t="s">
+      <c r="J4" s="165">
+        <v>45823</v>
+      </c>
+      <c r="K4" s="166"/>
+      <c r="L4" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="J4" s="141">
+      <c r="M4" s="167">
         <v>45823</v>
       </c>
-      <c r="K4" s="142"/>
-      <c r="L4" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="M4" s="143">
-        <v>45823</v>
-      </c>
-      <c r="N4" s="138"/>
+      <c r="N4" s="164"/>
     </row>
     <row r="5" spans="2:14" ht="58">
       <c r="B5" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="34">
         <v>420962</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E5" s="36">
         <v>45642</v>
       </c>
       <c r="F5" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="142" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="143"/>
+      <c r="I5" s="38" t="s">
         <v>129</v>
-      </c>
-      <c r="G5" s="139" t="s">
-        <v>124</v>
-      </c>
-      <c r="H5" s="140"/>
-      <c r="I5" s="38" t="s">
-        <v>130</v>
       </c>
       <c r="J5" s="144"/>
       <c r="K5" s="145"/>
       <c r="L5" s="39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M5" s="146"/>
       <c r="N5" s="147"/>
@@ -10260,48 +10251,48 @@
       <c r="I6" s="40"/>
       <c r="J6" s="40"/>
       <c r="L6" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="52.5" customHeight="1">
       <c r="B7" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="D7" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="E7" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="F7" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="F7" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="G7" s="42" t="s">
+      <c r="H7" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="I7" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="I7" s="42" t="s">
+      <c r="J7" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="J7" s="42" t="s">
+      <c r="K7" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="K7" s="44" t="s">
+      <c r="L7" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="L7" s="44" t="s">
+      <c r="M7" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="M7" s="44" t="s">
+      <c r="N7" s="45" t="s">
         <v>143</v>
-      </c>
-      <c r="N7" s="45" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="8" spans="2:14" s="24" customFormat="1" ht="67.5" customHeight="1">
@@ -10309,32 +10300,32 @@
         <v>1</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="F8" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="G8" s="49" t="s">
         <v>147</v>
-      </c>
-      <c r="G8" s="49" t="s">
-        <v>148</v>
       </c>
       <c r="H8" s="49"/>
       <c r="I8" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="J8" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="J8" s="50" t="s">
+      <c r="K8" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="K8" s="51" t="s">
+      <c r="L8" s="51" t="s">
         <v>151</v>
-      </c>
-      <c r="L8" s="51" t="s">
-        <v>152</v>
       </c>
       <c r="M8" s="52"/>
       <c r="N8" s="53"/>
@@ -10344,32 +10335,32 @@
         <v>2</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="48" t="s">
-        <v>154</v>
-      </c>
       <c r="F9" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="G9" s="49" t="s">
         <v>147</v>
-      </c>
-      <c r="G9" s="49" t="s">
-        <v>148</v>
       </c>
       <c r="H9" s="49"/>
       <c r="I9" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="J9" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="J9" s="50" t="s">
+      <c r="K9" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="K9" s="51" t="s">
+      <c r="L9" s="51" t="s">
         <v>151</v>
-      </c>
-      <c r="L9" s="51" t="s">
-        <v>152</v>
       </c>
       <c r="M9" s="52"/>
       <c r="N9" s="53"/>
@@ -10379,32 +10370,32 @@
         <v>3</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="E10" s="55" t="s">
+      <c r="F10" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="F10" s="49" t="s">
-        <v>157</v>
-      </c>
       <c r="G10" s="49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H10" s="49"/>
       <c r="I10" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="J10" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="J10" s="50" t="s">
-        <v>150</v>
-      </c>
       <c r="K10" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="L10" s="51" t="s">
         <v>158</v>
-      </c>
-      <c r="L10" s="51" t="s">
-        <v>159</v>
       </c>
       <c r="M10" s="52"/>
       <c r="N10" s="53"/>
@@ -10414,32 +10405,32 @@
         <v>4</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" s="56" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="E11" s="54" t="s">
-        <v>161</v>
-      </c>
       <c r="F11" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="G11" s="49" t="s">
         <v>147</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>148</v>
       </c>
       <c r="H11" s="49"/>
       <c r="I11" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="J11" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="50" t="s">
+      <c r="K11" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="K11" s="51" t="s">
+      <c r="L11" s="51" t="s">
         <v>151</v>
-      </c>
-      <c r="L11" s="51" t="s">
-        <v>152</v>
       </c>
       <c r="M11" s="52"/>
       <c r="N11" s="53"/>
@@ -10449,32 +10440,32 @@
         <v>5</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="E12" s="54" t="s">
-        <v>163</v>
-      </c>
       <c r="F12" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="49" t="s">
         <v>147</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>148</v>
       </c>
       <c r="H12" s="49"/>
       <c r="I12" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J12" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="K12" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="K12" s="51" t="s">
+      <c r="L12" s="51" t="s">
         <v>165</v>
-      </c>
-      <c r="L12" s="51" t="s">
-        <v>166</v>
       </c>
       <c r="M12" s="52"/>
       <c r="N12" s="53"/>
@@ -10484,32 +10475,32 @@
         <v>6</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" s="54" t="s">
+        <v>166</v>
+      </c>
+      <c r="E13" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="E13" s="54" t="s">
-        <v>168</v>
-      </c>
       <c r="F13" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H13" s="49"/>
       <c r="I13" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="J13" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="J13" s="50" t="s">
-        <v>150</v>
-      </c>
       <c r="K13" s="51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L13" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M13" s="52"/>
       <c r="N13" s="53"/>
@@ -10519,32 +10510,32 @@
         <v>7</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="E14" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="F14" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="G14" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H14" s="49"/>
       <c r="I14" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J14" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="K14" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="K14" s="51" t="s">
-        <v>175</v>
-      </c>
       <c r="L14" s="51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M14" s="52"/>
       <c r="N14" s="53"/>
@@ -10554,32 +10545,32 @@
         <v>8</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D15" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="56" t="s">
-        <v>177</v>
-      </c>
       <c r="F15" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G15" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H15" s="49"/>
       <c r="I15" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J15" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="K15" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="K15" s="51" t="s">
+      <c r="L15" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="L15" s="52" t="s">
-        <v>180</v>
       </c>
       <c r="M15" s="52"/>
       <c r="N15" s="53"/>
@@ -10589,32 +10580,32 @@
         <v>9</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="56" t="s">
         <v>181</v>
       </c>
-      <c r="E16" s="56" t="s">
-        <v>182</v>
-      </c>
       <c r="F16" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G16" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G16" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H16" s="49"/>
       <c r="I16" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J16" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="K16" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="K16" s="51" t="s">
+      <c r="L16" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="L16" s="52" t="s">
-        <v>180</v>
       </c>
       <c r="M16" s="52"/>
       <c r="N16" s="53"/>
@@ -10624,32 +10615,32 @@
         <v>10</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="E17" s="55" t="s">
-        <v>184</v>
-      </c>
       <c r="F17" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G17" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H17" s="49"/>
       <c r="I17" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J17" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="K17" s="51" t="s">
-        <v>186</v>
-      </c>
       <c r="L17" s="52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M17" s="52"/>
       <c r="N17" s="53"/>
@@ -10659,32 +10650,32 @@
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="E18" s="56" t="s">
-        <v>188</v>
-      </c>
       <c r="F18" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G18" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G18" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H18" s="49"/>
       <c r="I18" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J18" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K18" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="L18" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="L18" s="52" t="s">
-        <v>180</v>
       </c>
       <c r="M18" s="52"/>
       <c r="N18" s="53"/>
@@ -10694,32 +10685,32 @@
         <v>12</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19" s="54" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="56" t="s">
         <v>189</v>
       </c>
-      <c r="E19" s="56" t="s">
-        <v>190</v>
-      </c>
       <c r="F19" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H19" s="49"/>
       <c r="I19" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K19" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="L19" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="L19" s="52" t="s">
-        <v>180</v>
       </c>
       <c r="M19" s="52"/>
       <c r="N19" s="53"/>
@@ -10729,32 +10720,32 @@
         <v>13</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E20" s="56" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F20" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G20" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H20" s="49"/>
       <c r="I20" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J20" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K20" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="L20" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="L20" s="52" t="s">
-        <v>180</v>
       </c>
       <c r="M20" s="52"/>
       <c r="N20" s="53"/>
@@ -10764,32 +10755,32 @@
         <v>14</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" s="56" t="s">
         <v>192</v>
       </c>
-      <c r="E21" s="56" t="s">
-        <v>193</v>
-      </c>
       <c r="F21" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G21" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H21" s="49"/>
       <c r="I21" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J21" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K21" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="L21" s="51" t="s">
         <v>194</v>
-      </c>
-      <c r="L21" s="51" t="s">
-        <v>195</v>
       </c>
       <c r="M21" s="52"/>
       <c r="N21" s="53"/>
@@ -10799,32 +10790,32 @@
         <v>15</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E22" s="55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F22" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G22" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G22" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H22" s="49"/>
       <c r="I22" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J22" s="50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K22" s="51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L22" s="52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M22" s="52"/>
       <c r="N22" s="53"/>
@@ -10834,32 +10825,32 @@
         <v>16</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D23" s="54" t="s">
+        <v>197</v>
+      </c>
+      <c r="E23" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E23" s="29" t="s">
-        <v>199</v>
-      </c>
       <c r="F23" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H23" s="49"/>
       <c r="I23" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J23" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K23" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="L23" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="L23" s="52" t="s">
-        <v>180</v>
       </c>
       <c r="M23" s="52"/>
       <c r="N23" s="53"/>
@@ -10869,32 +10860,32 @@
         <v>17</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D24" s="54" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" s="57" t="s">
         <v>201</v>
       </c>
-      <c r="E24" s="57" t="s">
-        <v>202</v>
-      </c>
       <c r="F24" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G24" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H24" s="58"/>
       <c r="I24" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J24" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K24" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="L24" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="L24" s="52" t="s">
-        <v>180</v>
       </c>
       <c r="M24" s="59"/>
       <c r="N24" s="53"/>
@@ -10904,32 +10895,32 @@
         <v>18</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E25" s="57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F25" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G25" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G25" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H25" s="58"/>
       <c r="I25" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K25" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="L25" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="L25" s="52" t="s">
-        <v>180</v>
       </c>
       <c r="M25" s="59"/>
       <c r="N25" s="53"/>
@@ -10939,32 +10930,32 @@
         <v>19</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D26" s="54" t="s">
+        <v>204</v>
+      </c>
+      <c r="E26" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="57" t="s">
-        <v>206</v>
-      </c>
       <c r="F26" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G26" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G26" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="H26" s="58"/>
       <c r="I26" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J26" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K26" s="51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L26" s="52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M26" s="59"/>
       <c r="N26" s="53"/>
@@ -11083,7 +11074,7 @@
     <row r="35" spans="1:19" ht="14">
       <c r="A35" s="70"/>
       <c r="B35" s="71" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C35" s="71"/>
       <c r="D35" s="72"/>
@@ -11106,7 +11097,7 @@
     <row r="36" spans="1:19">
       <c r="A36" s="70"/>
       <c r="B36" s="71" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C36" s="71"/>
       <c r="D36" s="72"/>
@@ -11150,13 +11141,13 @@
     <row r="38" spans="1:19" ht="26.25" customHeight="1">
       <c r="A38" s="70"/>
       <c r="B38" s="151" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C38" s="152"/>
       <c r="D38" s="152"/>
       <c r="E38" s="153"/>
       <c r="F38" s="154" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G38" s="154"/>
       <c r="H38" s="154"/>
@@ -11179,14 +11170,14 @@
       <c r="D39" s="78"/>
       <c r="E39" s="79"/>
       <c r="F39" s="75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G39" s="80" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H39" s="79"/>
-      <c r="I39" s="156"/>
-      <c r="J39" s="156"/>
+      <c r="I39" s="135"/>
+      <c r="J39" s="135"/>
       <c r="K39" s="76"/>
       <c r="L39" s="76"/>
       <c r="M39" s="76"/>
@@ -11199,30 +11190,30 @@
     <row r="40" spans="1:19" ht="42" customHeight="1">
       <c r="A40" s="70"/>
       <c r="B40" s="81" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="C40" s="81" t="s">
+      <c r="D40" s="81" t="s">
         <v>212</v>
       </c>
-      <c r="D40" s="81" t="s">
+      <c r="E40" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="E40" s="81" t="s">
+      <c r="F40" s="81" t="s">
         <v>214</v>
       </c>
-      <c r="F40" s="81" t="s">
+      <c r="G40" s="81" t="s">
         <v>215</v>
       </c>
-      <c r="G40" s="81" t="s">
+      <c r="H40" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="H40" s="82" t="s">
+      <c r="I40" s="136" t="s">
         <v>217</v>
       </c>
-      <c r="I40" s="157" t="s">
-        <v>218</v>
-      </c>
-      <c r="J40" s="157"/>
+      <c r="J40" s="136"/>
       <c r="K40" s="76"/>
       <c r="L40" s="76"/>
       <c r="M40" s="76"/>
@@ -11256,7 +11247,7 @@
     <row r="42" spans="1:19">
       <c r="A42" s="70"/>
       <c r="B42" s="71" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C42" s="72"/>
       <c r="D42" s="72"/>
@@ -11300,16 +11291,16 @@
     <row r="44" spans="1:19" ht="36" customHeight="1">
       <c r="A44" s="70"/>
       <c r="B44" s="83" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="83" t="s">
         <v>220</v>
       </c>
-      <c r="C44" s="83" t="s">
+      <c r="D44" s="83" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="83" t="s">
-        <v>222</v>
-      </c>
       <c r="E44" s="75" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F44" s="72"/>
       <c r="G44" s="72"/>
@@ -11327,14 +11318,14 @@
     </row>
     <row r="45" spans="1:19" ht="34.5" customHeight="1">
       <c r="A45" s="70"/>
-      <c r="B45" s="158" t="s">
+      <c r="B45" s="137" t="s">
+        <v>222</v>
+      </c>
+      <c r="C45" s="85" t="s">
         <v>223</v>
       </c>
-      <c r="C45" s="85" t="s">
-        <v>224</v>
-      </c>
       <c r="D45" s="84" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E45" s="81"/>
       <c r="F45" s="72"/>
@@ -11353,12 +11344,12 @@
     </row>
     <row r="46" spans="1:19" ht="32.25" customHeight="1">
       <c r="A46" s="70"/>
-      <c r="B46" s="159"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="86" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D46" s="84" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E46" s="87"/>
       <c r="F46" s="72"/>
@@ -11377,14 +11368,14 @@
     </row>
     <row r="47" spans="1:19" ht="25.5" customHeight="1">
       <c r="A47" s="70"/>
-      <c r="B47" s="159"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="86" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D47" s="84" t="s">
-        <v>148</v>
-      </c>
-      <c r="E47" s="161"/>
+        <v>147</v>
+      </c>
+      <c r="E47" s="140"/>
       <c r="F47" s="72"/>
       <c r="G47" s="72"/>
       <c r="H47" s="72"/>
@@ -11401,14 +11392,14 @@
     </row>
     <row r="48" spans="1:19" ht="25.5" customHeight="1">
       <c r="A48" s="70"/>
-      <c r="B48" s="159"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="86" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D48" s="84" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="162"/>
+        <v>147</v>
+      </c>
+      <c r="E48" s="141"/>
       <c r="F48" s="72"/>
       <c r="G48" s="72"/>
       <c r="H48" s="72"/>
@@ -11425,15 +11416,15 @@
     </row>
     <row r="49" spans="1:19" ht="25.5" customHeight="1">
       <c r="A49" s="70"/>
-      <c r="B49" s="159"/>
+      <c r="B49" s="138"/>
       <c r="C49" s="86" t="s">
+        <v>227</v>
+      </c>
+      <c r="D49" s="84" t="s">
+        <v>147</v>
+      </c>
+      <c r="E49" s="88" t="s">
         <v>228</v>
-      </c>
-      <c r="D49" s="84" t="s">
-        <v>148</v>
-      </c>
-      <c r="E49" s="88" t="s">
-        <v>229</v>
       </c>
       <c r="F49" s="72"/>
       <c r="G49" s="72"/>
@@ -11451,16 +11442,16 @@
     </row>
     <row r="50" spans="1:19" ht="25.5" customHeight="1">
       <c r="A50" s="70"/>
-      <c r="B50" s="158" t="s">
-        <v>230</v>
+      <c r="B50" s="137" t="s">
+        <v>229</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D50" s="81" t="s">
-        <v>173</v>
-      </c>
-      <c r="E50" s="161"/>
+        <v>172</v>
+      </c>
+      <c r="E50" s="140"/>
       <c r="F50" s="72"/>
       <c r="G50" s="72"/>
       <c r="H50" s="72"/>
@@ -11477,14 +11468,14 @@
     </row>
     <row r="51" spans="1:19" ht="25.5" customHeight="1">
       <c r="A51" s="70"/>
-      <c r="B51" s="160"/>
+      <c r="B51" s="139"/>
       <c r="C51" s="86" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D51" s="81" t="s">
-        <v>173</v>
-      </c>
-      <c r="E51" s="162"/>
+        <v>172</v>
+      </c>
+      <c r="E51" s="141"/>
       <c r="F51" s="72"/>
       <c r="G51" s="72"/>
       <c r="H51" s="72"/>
@@ -11544,19 +11535,6 @@
   </sheetData>
   <autoFilter ref="B7:N51" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="21">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="B45:B49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D27:K27"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="F38:J38"/>
-    <mergeCell ref="D28:K31"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="J3:K3"/>
@@ -11565,6 +11543,19 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="D27:K27"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="D28:K31"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="E50:E51"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F26" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -11597,2013 +11588,2169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="40" customHeight="1">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="168" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
+      <c r="N1" s="168"/>
+      <c r="O1" s="168"/>
+      <c r="P1" s="168"/>
+      <c r="Q1" s="168"/>
+      <c r="R1" s="168"/>
+      <c r="S1" s="168"/>
+      <c r="T1" s="168"/>
+      <c r="U1" s="168"/>
+      <c r="V1" s="169"/>
+    </row>
+    <row r="2" spans="1:22" ht="40" customHeight="1">
+      <c r="A2" s="170"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
+      <c r="L2" s="170"/>
+      <c r="M2" s="170"/>
+      <c r="N2" s="170"/>
+      <c r="O2" s="170"/>
+      <c r="P2" s="170"/>
+      <c r="Q2" s="170"/>
+      <c r="R2" s="170"/>
+      <c r="S2" s="170"/>
+      <c r="T2" s="170"/>
+      <c r="U2" s="170"/>
+      <c r="V2" s="171"/>
+    </row>
+    <row r="3" spans="1:22" ht="40" customHeight="1">
+      <c r="A3" s="172" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="233"/>
-      <c r="U1" s="233"/>
-      <c r="V1" s="234"/>
-    </row>
-    <row r="2" spans="1:22" ht="40" customHeight="1">
-      <c r="A2" s="235"/>
-      <c r="B2" s="235"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="235"/>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="M2" s="235"/>
-      <c r="N2" s="235"/>
-      <c r="O2" s="235"/>
-      <c r="P2" s="235"/>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="268"/>
-    </row>
-    <row r="3" spans="1:22" ht="40" customHeight="1">
-      <c r="A3" s="238" t="s">
+      <c r="B3" s="173"/>
+      <c r="C3" s="176" t="s">
         <v>233</v>
       </c>
-      <c r="B3" s="221"/>
-      <c r="C3" s="271" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="263" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
-      <c r="F3" s="273"/>
-      <c r="G3" s="163" t="s">
+      <c r="H3" s="264"/>
+      <c r="I3" s="264"/>
+      <c r="J3" s="264"/>
+      <c r="K3" s="264"/>
+      <c r="L3" s="264"/>
+      <c r="M3" s="264"/>
+      <c r="N3" s="264"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="264"/>
+      <c r="Q3" s="264"/>
+      <c r="R3" s="264"/>
+      <c r="S3" s="265"/>
+      <c r="T3" s="236" t="s">
         <v>235</v>
       </c>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="164"/>
-      <c r="O3" s="164"/>
-      <c r="P3" s="164"/>
-      <c r="Q3" s="164"/>
-      <c r="R3" s="164"/>
-      <c r="S3" s="165"/>
-      <c r="T3" s="241" t="s">
+      <c r="U3" s="239" t="s">
         <v>236</v>
       </c>
-      <c r="U3" s="244" t="s">
+      <c r="V3" s="203" t="s">
         <v>237</v>
       </c>
-      <c r="V3" s="287" t="s">
+    </row>
+    <row r="4" spans="1:22" ht="40" customHeight="1">
+      <c r="A4" s="174"/>
+      <c r="B4" s="175"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="180"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="295" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" ht="40" customHeight="1">
-      <c r="A4" s="239"/>
-      <c r="B4" s="222"/>
-      <c r="C4" s="284"/>
-      <c r="D4" s="285"/>
-      <c r="E4" s="285"/>
-      <c r="F4" s="286"/>
-      <c r="G4" s="166" t="s">
+      <c r="H4" s="296"/>
+      <c r="I4" s="296"/>
+      <c r="J4" s="296"/>
+      <c r="K4" s="297"/>
+      <c r="L4" s="295" t="s">
         <v>239</v>
       </c>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="168"/>
-      <c r="L4" s="166" t="s">
+      <c r="M4" s="296"/>
+      <c r="N4" s="296"/>
+      <c r="O4" s="296"/>
+      <c r="P4" s="296"/>
+      <c r="Q4" s="296"/>
+      <c r="R4" s="296"/>
+      <c r="S4" s="297"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="240"/>
+      <c r="V4" s="204"/>
+    </row>
+    <row r="5" spans="1:22" ht="80" customHeight="1">
+      <c r="A5" s="230">
+        <v>1</v>
+      </c>
+      <c r="B5" s="231"/>
+      <c r="C5" s="188" t="s">
         <v>240</v>
       </c>
-      <c r="M4" s="167"/>
-      <c r="N4" s="167"/>
-      <c r="O4" s="167"/>
-      <c r="P4" s="167"/>
-      <c r="Q4" s="167"/>
-      <c r="R4" s="167"/>
-      <c r="S4" s="168"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="245"/>
-      <c r="V4" s="288"/>
-    </row>
-    <row r="5" spans="1:22" ht="80" customHeight="1">
-      <c r="A5" s="169">
-        <v>1</v>
-      </c>
-      <c r="B5" s="170"/>
-      <c r="C5" s="186" t="s">
+      <c r="D5" s="189"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="190"/>
+      <c r="G5" s="256" t="s">
         <v>241</v>
       </c>
-      <c r="D5" s="187"/>
-      <c r="E5" s="187"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="171" t="s">
+      <c r="H5" s="298"/>
+      <c r="I5" s="298"/>
+      <c r="J5" s="298"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="299" t="s">
         <v>242</v>
       </c>
-      <c r="H5" s="172"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="172"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="174" t="s">
+      <c r="M5" s="300"/>
+      <c r="N5" s="300"/>
+      <c r="O5" s="300"/>
+      <c r="P5" s="300"/>
+      <c r="Q5" s="300"/>
+      <c r="R5" s="300"/>
+      <c r="S5" s="301"/>
+      <c r="T5" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="M5" s="175"/>
-      <c r="N5" s="175"/>
-      <c r="O5" s="175"/>
-      <c r="P5" s="175"/>
-      <c r="Q5" s="175"/>
-      <c r="R5" s="175"/>
-      <c r="S5" s="176"/>
-      <c r="T5" s="3" t="s">
+      <c r="U5" s="229"/>
+      <c r="V5" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="U5" s="185"/>
-      <c r="V5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:22" ht="30" customHeight="1">
+      <c r="A6" s="230">
+        <v>2</v>
+      </c>
+      <c r="B6" s="231"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="190"/>
+      <c r="G6" s="302" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" ht="30" customHeight="1">
-      <c r="A6" s="169">
-        <v>2</v>
-      </c>
-      <c r="B6" s="170"/>
-      <c r="C6" s="186"/>
-      <c r="D6" s="187"/>
-      <c r="E6" s="187"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="177" t="s">
+      <c r="H6" s="302"/>
+      <c r="I6" s="302"/>
+      <c r="J6" s="302"/>
+      <c r="K6" s="302"/>
+      <c r="L6" s="294" t="s">
         <v>246</v>
       </c>
-      <c r="H6" s="177"/>
-      <c r="I6" s="177"/>
-      <c r="J6" s="177"/>
-      <c r="K6" s="177"/>
-      <c r="L6" s="178" t="s">
+      <c r="M6" s="294"/>
+      <c r="N6" s="294"/>
+      <c r="O6" s="294"/>
+      <c r="P6" s="294"/>
+      <c r="Q6" s="294"/>
+      <c r="R6" s="294"/>
+      <c r="S6" s="294"/>
+      <c r="T6" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U6" s="229"/>
+      <c r="V6" s="4"/>
+    </row>
+    <row r="7" spans="1:22" ht="30" customHeight="1">
+      <c r="A7" s="230">
+        <v>3</v>
+      </c>
+      <c r="B7" s="231"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="189"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="232" t="s">
         <v>247</v>
       </c>
-      <c r="M6" s="178"/>
-      <c r="N6" s="178"/>
-      <c r="O6" s="178"/>
-      <c r="P6" s="178"/>
-      <c r="Q6" s="178"/>
-      <c r="R6" s="178"/>
-      <c r="S6" s="178"/>
-      <c r="T6" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U6" s="185"/>
-      <c r="V6" s="4"/>
-    </row>
-    <row r="7" spans="1:22" ht="30" customHeight="1">
-      <c r="A7" s="169">
-        <v>3</v>
-      </c>
-      <c r="B7" s="170"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="187"/>
-      <c r="E7" s="187"/>
-      <c r="F7" s="188"/>
-      <c r="G7" s="189" t="s">
+      <c r="H7" s="232"/>
+      <c r="I7" s="232"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="232"/>
+      <c r="L7" s="294" t="s">
+        <v>246</v>
+      </c>
+      <c r="M7" s="294"/>
+      <c r="N7" s="294"/>
+      <c r="O7" s="294"/>
+      <c r="P7" s="294"/>
+      <c r="Q7" s="294"/>
+      <c r="R7" s="294"/>
+      <c r="S7" s="294"/>
+      <c r="T7" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U7" s="229"/>
+      <c r="V7" s="4"/>
+    </row>
+    <row r="8" spans="1:22" ht="66" customHeight="1">
+      <c r="A8" s="230">
+        <v>4</v>
+      </c>
+      <c r="B8" s="231"/>
+      <c r="C8" s="188"/>
+      <c r="D8" s="189"/>
+      <c r="E8" s="189"/>
+      <c r="F8" s="190"/>
+      <c r="G8" s="291" t="s">
         <v>248</v>
       </c>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="189"/>
-      <c r="K7" s="189"/>
-      <c r="L7" s="178" t="s">
-        <v>247</v>
-      </c>
-      <c r="M7" s="178"/>
-      <c r="N7" s="178"/>
-      <c r="O7" s="178"/>
-      <c r="P7" s="178"/>
-      <c r="Q7" s="178"/>
-      <c r="R7" s="178"/>
-      <c r="S7" s="178"/>
-      <c r="T7" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U7" s="185"/>
-      <c r="V7" s="4"/>
-    </row>
-    <row r="8" spans="1:22" ht="66" customHeight="1">
-      <c r="A8" s="169">
-        <v>4</v>
-      </c>
-      <c r="B8" s="170"/>
-      <c r="C8" s="186"/>
-      <c r="D8" s="187"/>
-      <c r="E8" s="187"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="179" t="s">
+      <c r="H8" s="292"/>
+      <c r="I8" s="292"/>
+      <c r="J8" s="292"/>
+      <c r="K8" s="293"/>
+      <c r="L8" s="233" t="s">
         <v>249</v>
       </c>
-      <c r="H8" s="180"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="182" t="s">
+      <c r="M8" s="234"/>
+      <c r="N8" s="234"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="234"/>
+      <c r="R8" s="234"/>
+      <c r="S8" s="235"/>
+      <c r="T8" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U8" s="229"/>
+      <c r="V8" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="M8" s="183"/>
-      <c r="N8" s="183"/>
-      <c r="O8" s="183"/>
-      <c r="P8" s="183"/>
-      <c r="Q8" s="183"/>
-      <c r="R8" s="183"/>
-      <c r="S8" s="184"/>
-      <c r="T8" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U8" s="185"/>
-      <c r="V8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:22" ht="53.25" customHeight="1">
+      <c r="A9" s="230">
+        <v>5</v>
+      </c>
+      <c r="B9" s="231"/>
+      <c r="C9" s="188"/>
+      <c r="D9" s="189"/>
+      <c r="E9" s="189"/>
+      <c r="F9" s="190"/>
+      <c r="G9" s="291" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" ht="53.25" customHeight="1">
-      <c r="A9" s="169">
-        <v>5</v>
-      </c>
-      <c r="B9" s="170"/>
-      <c r="C9" s="186"/>
-      <c r="D9" s="187"/>
-      <c r="E9" s="187"/>
-      <c r="F9" s="188"/>
-      <c r="G9" s="179" t="s">
+      <c r="H9" s="292"/>
+      <c r="I9" s="292"/>
+      <c r="J9" s="292"/>
+      <c r="K9" s="293"/>
+      <c r="L9" s="233" t="s">
         <v>252</v>
       </c>
-      <c r="H9" s="180"/>
-      <c r="I9" s="180"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="181"/>
-      <c r="L9" s="182" t="s">
+      <c r="M9" s="234"/>
+      <c r="N9" s="234"/>
+      <c r="O9" s="234"/>
+      <c r="P9" s="234"/>
+      <c r="Q9" s="234"/>
+      <c r="R9" s="234"/>
+      <c r="S9" s="235"/>
+      <c r="T9" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U9" s="229"/>
+      <c r="V9" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="48" customHeight="1">
+      <c r="A10" s="230">
+        <v>6</v>
+      </c>
+      <c r="B10" s="231"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="189"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="291" t="s">
         <v>253</v>
       </c>
-      <c r="M9" s="183"/>
-      <c r="N9" s="183"/>
-      <c r="O9" s="183"/>
-      <c r="P9" s="183"/>
-      <c r="Q9" s="183"/>
-      <c r="R9" s="183"/>
-      <c r="S9" s="184"/>
-      <c r="T9" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U9" s="185"/>
-      <c r="V9" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="48" customHeight="1">
-      <c r="A10" s="169">
-        <v>6</v>
-      </c>
-      <c r="B10" s="170"/>
-      <c r="C10" s="186"/>
-      <c r="D10" s="187"/>
-      <c r="E10" s="187"/>
-      <c r="F10" s="188"/>
-      <c r="G10" s="179" t="s">
+      <c r="H10" s="292"/>
+      <c r="I10" s="292"/>
+      <c r="J10" s="292"/>
+      <c r="K10" s="293"/>
+      <c r="L10" s="233" t="s">
         <v>254</v>
       </c>
-      <c r="H10" s="180"/>
-      <c r="I10" s="180"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="181"/>
-      <c r="L10" s="182" t="s">
+      <c r="M10" s="234"/>
+      <c r="N10" s="234"/>
+      <c r="O10" s="234"/>
+      <c r="P10" s="234"/>
+      <c r="Q10" s="234"/>
+      <c r="R10" s="234"/>
+      <c r="S10" s="235"/>
+      <c r="T10" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U10" s="229"/>
+      <c r="V10" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="51.75" customHeight="1">
+      <c r="A11" s="230">
+        <v>7</v>
+      </c>
+      <c r="B11" s="231"/>
+      <c r="C11" s="188"/>
+      <c r="D11" s="189"/>
+      <c r="E11" s="189"/>
+      <c r="F11" s="190"/>
+      <c r="G11" s="291" t="s">
         <v>255</v>
       </c>
-      <c r="M10" s="183"/>
-      <c r="N10" s="183"/>
-      <c r="O10" s="183"/>
-      <c r="P10" s="183"/>
-      <c r="Q10" s="183"/>
-      <c r="R10" s="183"/>
-      <c r="S10" s="184"/>
-      <c r="T10" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U10" s="185"/>
-      <c r="V10" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="51.75" customHeight="1">
-      <c r="A11" s="169">
-        <v>7</v>
-      </c>
-      <c r="B11" s="170"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="187"/>
-      <c r="F11" s="188"/>
-      <c r="G11" s="179" t="s">
+      <c r="H11" s="292"/>
+      <c r="I11" s="292"/>
+      <c r="J11" s="292"/>
+      <c r="K11" s="293"/>
+      <c r="L11" s="233" t="s">
         <v>256</v>
       </c>
-      <c r="H11" s="180"/>
-      <c r="I11" s="180"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="181"/>
-      <c r="L11" s="182" t="s">
-        <v>257</v>
-      </c>
-      <c r="M11" s="183"/>
-      <c r="N11" s="183"/>
-      <c r="O11" s="183"/>
-      <c r="P11" s="183"/>
-      <c r="Q11" s="183"/>
-      <c r="R11" s="183"/>
-      <c r="S11" s="184"/>
+      <c r="M11" s="234"/>
+      <c r="N11" s="234"/>
+      <c r="O11" s="234"/>
+      <c r="P11" s="234"/>
+      <c r="Q11" s="234"/>
+      <c r="R11" s="234"/>
+      <c r="S11" s="235"/>
       <c r="T11" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U11" s="185"/>
+        <v>243</v>
+      </c>
+      <c r="U11" s="229"/>
       <c r="V11" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="15">
       <c r="A12" s="5"/>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
+      <c r="B12" s="229"/>
+      <c r="C12" s="229"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="8"/>
-      <c r="J12" s="190" t="s">
+      <c r="J12" s="252" t="s">
+        <v>258</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="229"/>
+      <c r="M12" s="229"/>
+      <c r="N12" s="196" t="s">
         <v>259</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
-      <c r="N12" s="225" t="s">
+      <c r="O12" s="196"/>
+      <c r="P12" s="196"/>
+      <c r="Q12" s="196"/>
+      <c r="R12" s="196"/>
+      <c r="S12" s="196"/>
+      <c r="T12" s="245"/>
+      <c r="U12" s="199" t="s">
         <v>260</v>
       </c>
-      <c r="O12" s="225"/>
-      <c r="P12" s="225"/>
-      <c r="Q12" s="225"/>
-      <c r="R12" s="225"/>
-      <c r="S12" s="225"/>
-      <c r="T12" s="255"/>
-      <c r="U12" s="229" t="s">
-        <v>261</v>
-      </c>
-      <c r="V12" s="230"/>
+      <c r="V12" s="200"/>
     </row>
     <row r="13" spans="1:22" ht="15">
       <c r="A13" s="3"/>
-      <c r="B13" s="185"/>
-      <c r="C13" s="185"/>
+      <c r="B13" s="229"/>
+      <c r="C13" s="229"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="7"/>
       <c r="G13" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="190"/>
+      <c r="J13" s="252"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="185"/>
-      <c r="M13" s="185"/>
-      <c r="N13" s="226"/>
-      <c r="O13" s="226"/>
-      <c r="P13" s="226"/>
-      <c r="Q13" s="226"/>
-      <c r="R13" s="226"/>
-      <c r="S13" s="226"/>
-      <c r="T13" s="226"/>
-      <c r="U13" s="229"/>
-      <c r="V13" s="230"/>
+      <c r="L13" s="229"/>
+      <c r="M13" s="229"/>
+      <c r="N13" s="186"/>
+      <c r="O13" s="186"/>
+      <c r="P13" s="186"/>
+      <c r="Q13" s="186"/>
+      <c r="R13" s="186"/>
+      <c r="S13" s="186"/>
+      <c r="T13" s="186"/>
+      <c r="U13" s="199"/>
+      <c r="V13" s="200"/>
     </row>
     <row r="14" spans="1:22" ht="15">
       <c r="A14" s="3"/>
-      <c r="B14" s="185"/>
-      <c r="C14" s="185"/>
+      <c r="B14" s="229"/>
+      <c r="C14" s="229"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="7"/>
       <c r="G14" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="190"/>
+      <c r="J14" s="252"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="185"/>
-      <c r="M14" s="185"/>
-      <c r="N14" s="226"/>
-      <c r="O14" s="226"/>
-      <c r="P14" s="226"/>
-      <c r="Q14" s="226"/>
-      <c r="R14" s="226"/>
-      <c r="S14" s="226"/>
-      <c r="T14" s="226"/>
-      <c r="U14" s="231"/>
-      <c r="V14" s="232"/>
+      <c r="L14" s="229"/>
+      <c r="M14" s="229"/>
+      <c r="N14" s="186"/>
+      <c r="O14" s="186"/>
+      <c r="P14" s="186"/>
+      <c r="Q14" s="186"/>
+      <c r="R14" s="186"/>
+      <c r="S14" s="186"/>
+      <c r="T14" s="186"/>
+      <c r="U14" s="201"/>
+      <c r="V14" s="202"/>
     </row>
     <row r="15" spans="1:22" ht="15">
       <c r="A15" s="3"/>
-      <c r="B15" s="185"/>
-      <c r="C15" s="185"/>
+      <c r="B15" s="229"/>
+      <c r="C15" s="229"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="7"/>
       <c r="G15" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="190"/>
+      <c r="J15" s="252"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="190"/>
-      <c r="M15" s="190"/>
-      <c r="N15" s="226" t="s">
+      <c r="L15" s="252"/>
+      <c r="M15" s="252"/>
+      <c r="N15" s="186" t="s">
+        <v>264</v>
+      </c>
+      <c r="O15" s="186"/>
+      <c r="P15" s="186"/>
+      <c r="Q15" s="186"/>
+      <c r="R15" s="186"/>
+      <c r="S15" s="186"/>
+      <c r="T15" s="186"/>
+      <c r="U15" s="182" t="s">
         <v>265</v>
       </c>
-      <c r="O15" s="226"/>
-      <c r="P15" s="226"/>
-      <c r="Q15" s="226"/>
-      <c r="R15" s="226"/>
-      <c r="S15" s="226"/>
-      <c r="T15" s="226"/>
-      <c r="U15" s="251" t="s">
-        <v>266</v>
-      </c>
-      <c r="V15" s="252"/>
+      <c r="V15" s="183"/>
     </row>
     <row r="16" spans="1:22" ht="15">
       <c r="A16" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" s="253" t="s">
         <v>267</v>
       </c>
-      <c r="B16" s="191" t="s">
+      <c r="C16" s="253"/>
+      <c r="D16" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C16" s="191"/>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="F16" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="G16" s="254" t="s">
         <v>271</v>
       </c>
-      <c r="G16" s="192" t="s">
+      <c r="H16" s="254"/>
+      <c r="I16" s="254"/>
+      <c r="J16" s="254"/>
+      <c r="K16" s="253"/>
+      <c r="L16" s="253"/>
+      <c r="M16" s="253"/>
+      <c r="N16" s="187"/>
+      <c r="O16" s="187"/>
+      <c r="P16" s="187"/>
+      <c r="Q16" s="187"/>
+      <c r="R16" s="187"/>
+      <c r="S16" s="187"/>
+      <c r="T16" s="187"/>
+      <c r="U16" s="184"/>
+      <c r="V16" s="185"/>
+    </row>
+    <row r="17" spans="1:22" ht="40" customHeight="1">
+      <c r="A17" s="168" t="s">
+        <v>231</v>
+      </c>
+      <c r="B17" s="168"/>
+      <c r="C17" s="168"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="168"/>
+      <c r="H17" s="168"/>
+      <c r="I17" s="168"/>
+      <c r="J17" s="168"/>
+      <c r="K17" s="168"/>
+      <c r="L17" s="168"/>
+      <c r="M17" s="168"/>
+      <c r="N17" s="168"/>
+      <c r="O17" s="168"/>
+      <c r="P17" s="168"/>
+      <c r="Q17" s="168"/>
+      <c r="R17" s="168"/>
+      <c r="S17" s="168"/>
+      <c r="T17" s="168"/>
+      <c r="U17" s="168"/>
+      <c r="V17" s="169"/>
+    </row>
+    <row r="18" spans="1:22" ht="40" customHeight="1">
+      <c r="A18" s="170"/>
+      <c r="B18" s="170"/>
+      <c r="C18" s="289"/>
+      <c r="D18" s="289"/>
+      <c r="E18" s="289"/>
+      <c r="F18" s="289"/>
+      <c r="G18" s="170"/>
+      <c r="H18" s="170"/>
+      <c r="I18" s="170"/>
+      <c r="J18" s="170"/>
+      <c r="K18" s="170"/>
+      <c r="L18" s="170"/>
+      <c r="M18" s="170"/>
+      <c r="N18" s="170"/>
+      <c r="O18" s="170"/>
+      <c r="P18" s="170"/>
+      <c r="Q18" s="170"/>
+      <c r="R18" s="170"/>
+      <c r="S18" s="170"/>
+      <c r="T18" s="170"/>
+      <c r="U18" s="289"/>
+      <c r="V18" s="290"/>
+    </row>
+    <row r="19" spans="1:22" ht="40" customHeight="1">
+      <c r="A19" s="172" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="173"/>
+      <c r="C19" s="205" t="s">
+        <v>233</v>
+      </c>
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="205"/>
+      <c r="G19" s="263" t="s">
+        <v>234</v>
+      </c>
+      <c r="H19" s="264"/>
+      <c r="I19" s="264"/>
+      <c r="J19" s="264"/>
+      <c r="K19" s="264"/>
+      <c r="L19" s="264"/>
+      <c r="M19" s="264"/>
+      <c r="N19" s="264"/>
+      <c r="O19" s="264"/>
+      <c r="P19" s="264"/>
+      <c r="Q19" s="264"/>
+      <c r="R19" s="264"/>
+      <c r="S19" s="265"/>
+      <c r="T19" s="236" t="s">
+        <v>235</v>
+      </c>
+      <c r="U19" s="241" t="s">
+        <v>236</v>
+      </c>
+      <c r="V19" s="205" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="40" customHeight="1">
+      <c r="A20" s="174"/>
+      <c r="B20" s="175"/>
+      <c r="C20" s="205"/>
+      <c r="D20" s="205"/>
+      <c r="E20" s="205"/>
+      <c r="F20" s="205"/>
+      <c r="G20" s="266" t="s">
+        <v>238</v>
+      </c>
+      <c r="H20" s="267"/>
+      <c r="I20" s="267"/>
+      <c r="J20" s="267"/>
+      <c r="K20" s="268"/>
+      <c r="L20" s="266" t="s">
+        <v>239</v>
+      </c>
+      <c r="M20" s="267"/>
+      <c r="N20" s="267"/>
+      <c r="O20" s="267"/>
+      <c r="P20" s="267"/>
+      <c r="Q20" s="267"/>
+      <c r="R20" s="267"/>
+      <c r="S20" s="268"/>
+      <c r="T20" s="237"/>
+      <c r="U20" s="241"/>
+      <c r="V20" s="205"/>
+    </row>
+    <row r="21" spans="1:22" ht="80" customHeight="1">
+      <c r="A21" s="230">
+        <v>8</v>
+      </c>
+      <c r="B21" s="231"/>
+      <c r="C21" s="188" t="s">
+        <v>240</v>
+      </c>
+      <c r="D21" s="189"/>
+      <c r="E21" s="189"/>
+      <c r="F21" s="190"/>
+      <c r="G21" s="280" t="s">
         <v>272</v>
       </c>
-      <c r="H16" s="192"/>
-      <c r="I16" s="192"/>
-      <c r="J16" s="192"/>
-      <c r="K16" s="191"/>
-      <c r="L16" s="191"/>
-      <c r="M16" s="191"/>
-      <c r="N16" s="250"/>
-      <c r="O16" s="250"/>
-      <c r="P16" s="250"/>
-      <c r="Q16" s="250"/>
-      <c r="R16" s="250"/>
-      <c r="S16" s="250"/>
-      <c r="T16" s="250"/>
-      <c r="U16" s="253"/>
-      <c r="V16" s="254"/>
-    </row>
-    <row r="17" spans="1:22" ht="40" customHeight="1">
-      <c r="A17" s="233" t="s">
-        <v>232</v>
-      </c>
-      <c r="B17" s="233"/>
-      <c r="C17" s="233"/>
-      <c r="D17" s="233"/>
-      <c r="E17" s="233"/>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="233"/>
-      <c r="L17" s="233"/>
-      <c r="M17" s="233"/>
-      <c r="N17" s="233"/>
-      <c r="O17" s="233"/>
-      <c r="P17" s="233"/>
-      <c r="Q17" s="233"/>
-      <c r="R17" s="233"/>
-      <c r="S17" s="233"/>
-      <c r="T17" s="233"/>
-      <c r="U17" s="233"/>
-      <c r="V17" s="234"/>
-    </row>
-    <row r="18" spans="1:22" ht="40" customHeight="1">
-      <c r="A18" s="235"/>
-      <c r="B18" s="235"/>
-      <c r="C18" s="236"/>
-      <c r="D18" s="236"/>
-      <c r="E18" s="236"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
-      <c r="M18" s="235"/>
-      <c r="N18" s="235"/>
-      <c r="O18" s="235"/>
-      <c r="P18" s="235"/>
-      <c r="Q18" s="235"/>
-      <c r="R18" s="235"/>
-      <c r="S18" s="235"/>
-      <c r="T18" s="235"/>
-      <c r="U18" s="236"/>
-      <c r="V18" s="237"/>
-    </row>
-    <row r="19" spans="1:22" ht="40" customHeight="1">
-      <c r="A19" s="238" t="s">
-        <v>233</v>
-      </c>
-      <c r="B19" s="221"/>
-      <c r="C19" s="240" t="s">
-        <v>234</v>
-      </c>
-      <c r="D19" s="240"/>
-      <c r="E19" s="240"/>
-      <c r="F19" s="240"/>
-      <c r="G19" s="163" t="s">
-        <v>235</v>
-      </c>
-      <c r="H19" s="164"/>
-      <c r="I19" s="164"/>
-      <c r="J19" s="164"/>
-      <c r="K19" s="164"/>
-      <c r="L19" s="164"/>
-      <c r="M19" s="164"/>
-      <c r="N19" s="164"/>
-      <c r="O19" s="164"/>
-      <c r="P19" s="164"/>
-      <c r="Q19" s="164"/>
-      <c r="R19" s="164"/>
-      <c r="S19" s="165"/>
-      <c r="T19" s="241" t="s">
-        <v>236</v>
-      </c>
-      <c r="U19" s="246" t="s">
-        <v>237</v>
-      </c>
-      <c r="V19" s="240" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="40" customHeight="1">
-      <c r="A20" s="239"/>
-      <c r="B20" s="222"/>
-      <c r="C20" s="240"/>
-      <c r="D20" s="240"/>
-      <c r="E20" s="240"/>
-      <c r="F20" s="240"/>
-      <c r="G20" s="193" t="s">
-        <v>239</v>
-      </c>
-      <c r="H20" s="194"/>
-      <c r="I20" s="194"/>
-      <c r="J20" s="194"/>
-      <c r="K20" s="195"/>
-      <c r="L20" s="193" t="s">
-        <v>240</v>
-      </c>
-      <c r="M20" s="194"/>
-      <c r="N20" s="194"/>
-      <c r="O20" s="194"/>
-      <c r="P20" s="194"/>
-      <c r="Q20" s="194"/>
-      <c r="R20" s="194"/>
-      <c r="S20" s="195"/>
-      <c r="T20" s="242"/>
-      <c r="U20" s="246"/>
-      <c r="V20" s="240"/>
-    </row>
-    <row r="21" spans="1:22" ht="80" customHeight="1">
-      <c r="A21" s="169">
-        <v>8</v>
-      </c>
-      <c r="B21" s="170"/>
-      <c r="C21" s="186" t="s">
-        <v>241</v>
-      </c>
-      <c r="D21" s="187"/>
-      <c r="E21" s="187"/>
-      <c r="F21" s="188"/>
-      <c r="G21" s="196" t="s">
+      <c r="H21" s="281"/>
+      <c r="I21" s="281"/>
+      <c r="J21" s="281"/>
+      <c r="K21" s="281"/>
+      <c r="L21" s="286" t="s">
         <v>273</v>
       </c>
-      <c r="H21" s="197"/>
-      <c r="I21" s="197"/>
-      <c r="J21" s="197"/>
-      <c r="K21" s="197"/>
-      <c r="L21" s="202" t="s">
+      <c r="M21" s="287"/>
+      <c r="N21" s="287"/>
+      <c r="O21" s="287"/>
+      <c r="P21" s="287"/>
+      <c r="Q21" s="287"/>
+      <c r="R21" s="287"/>
+      <c r="S21" s="288"/>
+      <c r="T21" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U21" s="242"/>
+      <c r="V21" s="11" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="50" customHeight="1">
+      <c r="A22" s="230">
+        <v>9</v>
+      </c>
+      <c r="B22" s="231"/>
+      <c r="C22" s="188"/>
+      <c r="D22" s="189"/>
+      <c r="E22" s="189"/>
+      <c r="F22" s="190"/>
+      <c r="G22" s="280" t="s">
         <v>274</v>
       </c>
-      <c r="M21" s="203"/>
-      <c r="N21" s="203"/>
-      <c r="O21" s="203"/>
-      <c r="P21" s="203"/>
-      <c r="Q21" s="203"/>
-      <c r="R21" s="203"/>
-      <c r="S21" s="204"/>
-      <c r="T21" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U21" s="247"/>
-      <c r="V21" s="11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="50" customHeight="1">
-      <c r="A22" s="169">
-        <v>9</v>
-      </c>
-      <c r="B22" s="170"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="187"/>
-      <c r="E22" s="187"/>
-      <c r="F22" s="188"/>
-      <c r="G22" s="196" t="s">
+      <c r="H22" s="281"/>
+      <c r="I22" s="281"/>
+      <c r="J22" s="281"/>
+      <c r="K22" s="281"/>
+      <c r="L22" s="286" t="s">
         <v>275</v>
       </c>
-      <c r="H22" s="197"/>
-      <c r="I22" s="197"/>
-      <c r="J22" s="197"/>
-      <c r="K22" s="197"/>
-      <c r="L22" s="202" t="s">
+      <c r="M22" s="287"/>
+      <c r="N22" s="287"/>
+      <c r="O22" s="287"/>
+      <c r="P22" s="287"/>
+      <c r="Q22" s="287"/>
+      <c r="R22" s="287"/>
+      <c r="S22" s="288"/>
+      <c r="T22" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U22" s="242"/>
+      <c r="V22" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="M22" s="203"/>
-      <c r="N22" s="203"/>
-      <c r="O22" s="203"/>
-      <c r="P22" s="203"/>
-      <c r="Q22" s="203"/>
-      <c r="R22" s="203"/>
-      <c r="S22" s="204"/>
-      <c r="T22" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U22" s="247"/>
-      <c r="V22" s="12" t="s">
+    </row>
+    <row r="23" spans="1:22" ht="50" customHeight="1">
+      <c r="A23" s="230">
+        <v>10</v>
+      </c>
+      <c r="B23" s="231"/>
+      <c r="C23" s="188"/>
+      <c r="D23" s="189"/>
+      <c r="E23" s="189"/>
+      <c r="F23" s="190"/>
+      <c r="G23" s="280" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" ht="50" customHeight="1">
-      <c r="A23" s="169">
-        <v>10</v>
-      </c>
-      <c r="B23" s="170"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="187"/>
-      <c r="E23" s="187"/>
-      <c r="F23" s="188"/>
-      <c r="G23" s="196" t="s">
+      <c r="H23" s="281"/>
+      <c r="I23" s="281"/>
+      <c r="J23" s="281"/>
+      <c r="K23" s="281"/>
+      <c r="L23" s="286" t="s">
         <v>278</v>
       </c>
-      <c r="H23" s="197"/>
-      <c r="I23" s="197"/>
-      <c r="J23" s="197"/>
-      <c r="K23" s="197"/>
-      <c r="L23" s="202" t="s">
+      <c r="M23" s="287"/>
+      <c r="N23" s="287"/>
+      <c r="O23" s="287"/>
+      <c r="P23" s="287"/>
+      <c r="Q23" s="287"/>
+      <c r="R23" s="287"/>
+      <c r="S23" s="288"/>
+      <c r="T23" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U23" s="242"/>
+      <c r="V23" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="M23" s="203"/>
-      <c r="N23" s="203"/>
-      <c r="O23" s="203"/>
-      <c r="P23" s="203"/>
-      <c r="Q23" s="203"/>
-      <c r="R23" s="203"/>
-      <c r="S23" s="204"/>
-      <c r="T23" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U23" s="247"/>
-      <c r="V23" s="12" t="s">
+    </row>
+    <row r="24" spans="1:22" ht="50" customHeight="1">
+      <c r="A24" s="230">
+        <v>11</v>
+      </c>
+      <c r="B24" s="231"/>
+      <c r="C24" s="188"/>
+      <c r="D24" s="189"/>
+      <c r="E24" s="189"/>
+      <c r="F24" s="190"/>
+      <c r="G24" s="232" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" ht="50" customHeight="1">
-      <c r="A24" s="169">
-        <v>11</v>
-      </c>
-      <c r="B24" s="170"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="187"/>
-      <c r="E24" s="187"/>
-      <c r="F24" s="188"/>
-      <c r="G24" s="189" t="s">
+      <c r="H24" s="232"/>
+      <c r="I24" s="232"/>
+      <c r="J24" s="232"/>
+      <c r="K24" s="232"/>
+      <c r="L24" s="233"/>
+      <c r="M24" s="234"/>
+      <c r="N24" s="234"/>
+      <c r="O24" s="234"/>
+      <c r="P24" s="234"/>
+      <c r="Q24" s="234"/>
+      <c r="R24" s="234"/>
+      <c r="S24" s="235"/>
+      <c r="T24" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U24" s="242"/>
+      <c r="V24" s="12"/>
+    </row>
+    <row r="25" spans="1:22" ht="50" customHeight="1">
+      <c r="A25" s="230">
+        <v>12</v>
+      </c>
+      <c r="B25" s="231"/>
+      <c r="C25" s="188"/>
+      <c r="D25" s="189"/>
+      <c r="E25" s="189"/>
+      <c r="F25" s="190"/>
+      <c r="G25" s="232" t="s">
         <v>281</v>
       </c>
-      <c r="H24" s="189"/>
-      <c r="I24" s="189"/>
-      <c r="J24" s="189"/>
-      <c r="K24" s="189"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="183"/>
-      <c r="N24" s="183"/>
-      <c r="O24" s="183"/>
-      <c r="P24" s="183"/>
-      <c r="Q24" s="183"/>
-      <c r="R24" s="183"/>
-      <c r="S24" s="184"/>
-      <c r="T24" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U24" s="247"/>
-      <c r="V24" s="12"/>
-    </row>
-    <row r="25" spans="1:22" ht="50" customHeight="1">
-      <c r="A25" s="169">
-        <v>12</v>
-      </c>
-      <c r="B25" s="170"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="187"/>
-      <c r="E25" s="187"/>
-      <c r="F25" s="188"/>
-      <c r="G25" s="189" t="s">
+      <c r="H25" s="232"/>
+      <c r="I25" s="232"/>
+      <c r="J25" s="232"/>
+      <c r="K25" s="232"/>
+      <c r="L25" s="233"/>
+      <c r="M25" s="234"/>
+      <c r="N25" s="234"/>
+      <c r="O25" s="234"/>
+      <c r="P25" s="234"/>
+      <c r="Q25" s="234"/>
+      <c r="R25" s="234"/>
+      <c r="S25" s="235"/>
+      <c r="T25" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U25" s="242"/>
+      <c r="V25" s="12"/>
+    </row>
+    <row r="26" spans="1:22" ht="30" customHeight="1">
+      <c r="A26" s="230">
+        <v>13</v>
+      </c>
+      <c r="B26" s="231"/>
+      <c r="C26" s="188"/>
+      <c r="D26" s="189"/>
+      <c r="E26" s="189"/>
+      <c r="F26" s="190"/>
+      <c r="G26" s="280" t="s">
         <v>282</v>
       </c>
-      <c r="H25" s="189"/>
-      <c r="I25" s="189"/>
-      <c r="J25" s="189"/>
-      <c r="K25" s="189"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="183"/>
-      <c r="N25" s="183"/>
-      <c r="O25" s="183"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="183"/>
-      <c r="R25" s="183"/>
-      <c r="S25" s="184"/>
-      <c r="T25" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U25" s="247"/>
-      <c r="V25" s="12"/>
-    </row>
-    <row r="26" spans="1:22" ht="30" customHeight="1">
-      <c r="A26" s="169">
-        <v>13</v>
-      </c>
-      <c r="B26" s="170"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="187"/>
-      <c r="E26" s="187"/>
-      <c r="F26" s="188"/>
-      <c r="G26" s="196" t="s">
+      <c r="H26" s="281"/>
+      <c r="I26" s="281"/>
+      <c r="J26" s="281"/>
+      <c r="K26" s="282"/>
+      <c r="L26" s="283" t="s">
         <v>283</v>
       </c>
-      <c r="H26" s="197"/>
-      <c r="I26" s="197"/>
-      <c r="J26" s="197"/>
-      <c r="K26" s="198"/>
-      <c r="L26" s="199" t="s">
+      <c r="M26" s="284"/>
+      <c r="N26" s="284"/>
+      <c r="O26" s="284"/>
+      <c r="P26" s="284"/>
+      <c r="Q26" s="284"/>
+      <c r="R26" s="284"/>
+      <c r="S26" s="285"/>
+      <c r="T26" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="U26" s="242"/>
+      <c r="V26" s="12"/>
+    </row>
+    <row r="27" spans="1:22" ht="30" customHeight="1">
+      <c r="A27" s="221">
+        <v>14</v>
+      </c>
+      <c r="B27" s="222"/>
+      <c r="C27" s="188"/>
+      <c r="D27" s="189"/>
+      <c r="E27" s="189"/>
+      <c r="F27" s="190"/>
+      <c r="G27" s="223" t="s">
         <v>284</v>
       </c>
-      <c r="M26" s="200"/>
-      <c r="N26" s="200"/>
-      <c r="O26" s="200"/>
-      <c r="P26" s="200"/>
-      <c r="Q26" s="200"/>
-      <c r="R26" s="200"/>
-      <c r="S26" s="201"/>
-      <c r="T26" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U26" s="247"/>
-      <c r="V26" s="12"/>
-    </row>
-    <row r="27" spans="1:22" ht="30" customHeight="1">
-      <c r="A27" s="277">
-        <v>14</v>
-      </c>
-      <c r="B27" s="278"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="187"/>
-      <c r="E27" s="187"/>
-      <c r="F27" s="188"/>
-      <c r="G27" s="279" t="s">
+      <c r="H27" s="224"/>
+      <c r="I27" s="224"/>
+      <c r="J27" s="224"/>
+      <c r="K27" s="224"/>
+      <c r="L27" s="225" t="s">
         <v>285</v>
       </c>
-      <c r="H27" s="280"/>
-      <c r="I27" s="280"/>
-      <c r="J27" s="280"/>
-      <c r="K27" s="280"/>
-      <c r="L27" s="281" t="s">
-        <v>286</v>
-      </c>
-      <c r="M27" s="282"/>
-      <c r="N27" s="282"/>
-      <c r="O27" s="282"/>
-      <c r="P27" s="282"/>
-      <c r="Q27" s="282"/>
-      <c r="R27" s="282"/>
-      <c r="S27" s="283"/>
+      <c r="M27" s="226"/>
+      <c r="N27" s="226"/>
+      <c r="O27" s="226"/>
+      <c r="P27" s="226"/>
+      <c r="Q27" s="226"/>
+      <c r="R27" s="226"/>
+      <c r="S27" s="227"/>
       <c r="T27" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="U27" s="247"/>
+        <v>243</v>
+      </c>
+      <c r="U27" s="242"/>
       <c r="V27" s="12"/>
     </row>
     <row r="28" spans="1:22" ht="15">
       <c r="A28" s="14"/>
-      <c r="B28" s="220"/>
-      <c r="C28" s="220"/>
+      <c r="B28" s="228"/>
+      <c r="C28" s="228"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
       <c r="G28" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="18"/>
-      <c r="J28" s="216" t="s">
-        <v>259</v>
+      <c r="J28" s="255" t="s">
+        <v>258</v>
       </c>
       <c r="K28" s="17"/>
-      <c r="L28" s="220"/>
-      <c r="M28" s="220"/>
-      <c r="N28" s="225" t="s">
-        <v>287</v>
-      </c>
-      <c r="O28" s="225"/>
-      <c r="P28" s="225"/>
-      <c r="Q28" s="225"/>
-      <c r="R28" s="225"/>
-      <c r="S28" s="225"/>
-      <c r="T28" s="225"/>
-      <c r="U28" s="227" t="s">
-        <v>261</v>
-      </c>
-      <c r="V28" s="228"/>
+      <c r="L28" s="228"/>
+      <c r="M28" s="228"/>
+      <c r="N28" s="196" t="s">
+        <v>286</v>
+      </c>
+      <c r="O28" s="196"/>
+      <c r="P28" s="196"/>
+      <c r="Q28" s="196"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="196"/>
+      <c r="T28" s="196"/>
+      <c r="U28" s="197" t="s">
+        <v>260</v>
+      </c>
+      <c r="V28" s="198"/>
     </row>
     <row r="29" spans="1:22" ht="15">
       <c r="A29" s="19"/>
-      <c r="B29" s="185"/>
-      <c r="C29" s="185"/>
+      <c r="B29" s="229"/>
+      <c r="C29" s="229"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="7"/>
       <c r="G29" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="8"/>
-      <c r="J29" s="190"/>
+      <c r="J29" s="252"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="185"/>
-      <c r="M29" s="185"/>
-      <c r="N29" s="226"/>
-      <c r="O29" s="226"/>
-      <c r="P29" s="226"/>
-      <c r="Q29" s="226"/>
-      <c r="R29" s="226"/>
-      <c r="S29" s="226"/>
-      <c r="T29" s="226"/>
-      <c r="U29" s="229"/>
-      <c r="V29" s="230"/>
+      <c r="L29" s="229"/>
+      <c r="M29" s="229"/>
+      <c r="N29" s="186"/>
+      <c r="O29" s="186"/>
+      <c r="P29" s="186"/>
+      <c r="Q29" s="186"/>
+      <c r="R29" s="186"/>
+      <c r="S29" s="186"/>
+      <c r="T29" s="186"/>
+      <c r="U29" s="199"/>
+      <c r="V29" s="200"/>
     </row>
     <row r="30" spans="1:22" ht="15">
       <c r="A30" s="19"/>
-      <c r="B30" s="185"/>
-      <c r="C30" s="185"/>
+      <c r="B30" s="229"/>
+      <c r="C30" s="229"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="7"/>
       <c r="G30" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="190"/>
+      <c r="J30" s="252"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="185"/>
-      <c r="M30" s="185"/>
-      <c r="N30" s="226"/>
-      <c r="O30" s="226"/>
-      <c r="P30" s="226"/>
-      <c r="Q30" s="226"/>
-      <c r="R30" s="226"/>
-      <c r="S30" s="226"/>
-      <c r="T30" s="226"/>
-      <c r="U30" s="231"/>
-      <c r="V30" s="232"/>
+      <c r="L30" s="229"/>
+      <c r="M30" s="229"/>
+      <c r="N30" s="186"/>
+      <c r="O30" s="186"/>
+      <c r="P30" s="186"/>
+      <c r="Q30" s="186"/>
+      <c r="R30" s="186"/>
+      <c r="S30" s="186"/>
+      <c r="T30" s="186"/>
+      <c r="U30" s="201"/>
+      <c r="V30" s="202"/>
     </row>
     <row r="31" spans="1:22" ht="15">
       <c r="A31" s="19"/>
-      <c r="B31" s="185"/>
-      <c r="C31" s="185"/>
+      <c r="B31" s="229"/>
+      <c r="C31" s="229"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="7"/>
       <c r="G31" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="190"/>
+      <c r="J31" s="252"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="190"/>
-      <c r="M31" s="190"/>
-      <c r="N31" s="226" t="s">
+      <c r="L31" s="252"/>
+      <c r="M31" s="252"/>
+      <c r="N31" s="186" t="s">
+        <v>264</v>
+      </c>
+      <c r="O31" s="186"/>
+      <c r="P31" s="186"/>
+      <c r="Q31" s="186"/>
+      <c r="R31" s="186"/>
+      <c r="S31" s="186"/>
+      <c r="T31" s="186"/>
+      <c r="U31" s="182" t="s">
         <v>265</v>
       </c>
-      <c r="O31" s="226"/>
-      <c r="P31" s="226"/>
-      <c r="Q31" s="226"/>
-      <c r="R31" s="226"/>
-      <c r="S31" s="226"/>
-      <c r="T31" s="226"/>
-      <c r="U31" s="251" t="s">
-        <v>266</v>
-      </c>
-      <c r="V31" s="252"/>
+      <c r="V31" s="183"/>
     </row>
     <row r="32" spans="1:22" ht="15">
       <c r="A32" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="B32" s="253" t="s">
         <v>267</v>
       </c>
-      <c r="B32" s="191" t="s">
+      <c r="C32" s="253"/>
+      <c r="D32" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C32" s="191"/>
-      <c r="D32" s="10" t="s">
+      <c r="E32" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="F32" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="G32" s="254" t="s">
         <v>271</v>
       </c>
-      <c r="G32" s="192" t="s">
-        <v>272</v>
-      </c>
-      <c r="H32" s="192"/>
-      <c r="I32" s="192"/>
-      <c r="J32" s="192"/>
-      <c r="K32" s="191"/>
-      <c r="L32" s="191"/>
-      <c r="M32" s="191"/>
-      <c r="N32" s="250"/>
-      <c r="O32" s="250"/>
-      <c r="P32" s="250"/>
-      <c r="Q32" s="250"/>
-      <c r="R32" s="250"/>
-      <c r="S32" s="250"/>
-      <c r="T32" s="250"/>
-      <c r="U32" s="253"/>
-      <c r="V32" s="254"/>
+      <c r="H32" s="254"/>
+      <c r="I32" s="254"/>
+      <c r="J32" s="254"/>
+      <c r="K32" s="253"/>
+      <c r="L32" s="253"/>
+      <c r="M32" s="253"/>
+      <c r="N32" s="187"/>
+      <c r="O32" s="187"/>
+      <c r="P32" s="187"/>
+      <c r="Q32" s="187"/>
+      <c r="R32" s="187"/>
+      <c r="S32" s="187"/>
+      <c r="T32" s="187"/>
+      <c r="U32" s="184"/>
+      <c r="V32" s="185"/>
     </row>
     <row r="33" spans="1:25" ht="40" customHeight="1">
-      <c r="A33" s="233" t="s">
+      <c r="A33" s="168" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" s="168"/>
+      <c r="C33" s="168"/>
+      <c r="D33" s="168"/>
+      <c r="E33" s="168"/>
+      <c r="F33" s="168"/>
+      <c r="G33" s="168"/>
+      <c r="H33" s="168"/>
+      <c r="I33" s="168"/>
+      <c r="J33" s="168"/>
+      <c r="K33" s="168"/>
+      <c r="L33" s="168"/>
+      <c r="M33" s="168"/>
+      <c r="N33" s="168"/>
+      <c r="O33" s="168"/>
+      <c r="P33" s="168"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="168"/>
+      <c r="S33" s="168"/>
+      <c r="T33" s="168"/>
+      <c r="U33" s="168"/>
+      <c r="V33" s="169"/>
+    </row>
+    <row r="34" spans="1:25" ht="40" customHeight="1">
+      <c r="A34" s="170"/>
+      <c r="B34" s="170"/>
+      <c r="C34" s="170"/>
+      <c r="D34" s="170"/>
+      <c r="E34" s="170"/>
+      <c r="F34" s="170"/>
+      <c r="G34" s="170"/>
+      <c r="H34" s="170"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="170"/>
+      <c r="K34" s="170"/>
+      <c r="L34" s="170"/>
+      <c r="M34" s="170"/>
+      <c r="N34" s="170"/>
+      <c r="O34" s="170"/>
+      <c r="P34" s="170"/>
+      <c r="Q34" s="170"/>
+      <c r="R34" s="170"/>
+      <c r="S34" s="170"/>
+      <c r="T34" s="170"/>
+      <c r="U34" s="170"/>
+      <c r="V34" s="171"/>
+    </row>
+    <row r="35" spans="1:25" ht="40" customHeight="1">
+      <c r="A35" s="172" t="s">
         <v>232</v>
       </c>
-      <c r="B33" s="233"/>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
-      <c r="I33" s="233"/>
-      <c r="J33" s="233"/>
-      <c r="K33" s="233"/>
-      <c r="L33" s="233"/>
-      <c r="M33" s="233"/>
-      <c r="N33" s="233"/>
-      <c r="O33" s="233"/>
-      <c r="P33" s="233"/>
-      <c r="Q33" s="233"/>
-      <c r="R33" s="233"/>
-      <c r="S33" s="233"/>
-      <c r="T33" s="233"/>
-      <c r="U33" s="233"/>
-      <c r="V33" s="234"/>
-    </row>
-    <row r="34" spans="1:25" ht="40" customHeight="1">
-      <c r="A34" s="235"/>
-      <c r="B34" s="235"/>
-      <c r="C34" s="235"/>
-      <c r="D34" s="235"/>
-      <c r="E34" s="235"/>
-      <c r="F34" s="235"/>
-      <c r="G34" s="235"/>
-      <c r="H34" s="235"/>
-      <c r="I34" s="235"/>
-      <c r="J34" s="235"/>
-      <c r="K34" s="235"/>
-      <c r="L34" s="235"/>
-      <c r="M34" s="235"/>
-      <c r="N34" s="235"/>
-      <c r="O34" s="235"/>
-      <c r="P34" s="235"/>
-      <c r="Q34" s="235"/>
-      <c r="R34" s="235"/>
-      <c r="S34" s="235"/>
-      <c r="T34" s="235"/>
-      <c r="U34" s="235"/>
-      <c r="V34" s="268"/>
-    </row>
-    <row r="35" spans="1:25" ht="40" customHeight="1">
-      <c r="A35" s="238" t="s">
+      <c r="B35" s="173"/>
+      <c r="C35" s="176" t="s">
         <v>233</v>
       </c>
-      <c r="B35" s="221"/>
-      <c r="C35" s="271" t="s">
+      <c r="D35" s="177"/>
+      <c r="E35" s="177"/>
+      <c r="F35" s="178"/>
+      <c r="G35" s="263" t="s">
         <v>234</v>
       </c>
-      <c r="D35" s="272"/>
-      <c r="E35" s="272"/>
-      <c r="F35" s="273"/>
-      <c r="G35" s="163" t="s">
+      <c r="H35" s="264"/>
+      <c r="I35" s="264"/>
+      <c r="J35" s="264"/>
+      <c r="K35" s="264"/>
+      <c r="L35" s="264"/>
+      <c r="M35" s="264"/>
+      <c r="N35" s="264"/>
+      <c r="O35" s="264"/>
+      <c r="P35" s="264"/>
+      <c r="Q35" s="264"/>
+      <c r="R35" s="264"/>
+      <c r="S35" s="265"/>
+      <c r="T35" s="236" t="s">
         <v>235</v>
       </c>
-      <c r="H35" s="164"/>
-      <c r="I35" s="164"/>
-      <c r="J35" s="164"/>
-      <c r="K35" s="164"/>
-      <c r="L35" s="164"/>
-      <c r="M35" s="164"/>
-      <c r="N35" s="164"/>
-      <c r="O35" s="164"/>
-      <c r="P35" s="164"/>
-      <c r="Q35" s="164"/>
-      <c r="R35" s="164"/>
-      <c r="S35" s="165"/>
-      <c r="T35" s="241" t="s">
+      <c r="U35" s="239" t="s">
         <v>236</v>
       </c>
-      <c r="U35" s="244" t="s">
+      <c r="V35" s="203" t="s">
         <v>237</v>
       </c>
-      <c r="V35" s="287" t="s">
+    </row>
+    <row r="36" spans="1:25" ht="40" customHeight="1">
+      <c r="A36" s="191"/>
+      <c r="B36" s="192"/>
+      <c r="C36" s="193"/>
+      <c r="D36" s="194"/>
+      <c r="E36" s="194"/>
+      <c r="F36" s="195"/>
+      <c r="G36" s="266" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="36" spans="1:25" ht="40" customHeight="1">
-      <c r="A36" s="269"/>
-      <c r="B36" s="270"/>
-      <c r="C36" s="274"/>
-      <c r="D36" s="275"/>
-      <c r="E36" s="275"/>
-      <c r="F36" s="276"/>
-      <c r="G36" s="193" t="s">
+      <c r="H36" s="267"/>
+      <c r="I36" s="267"/>
+      <c r="J36" s="267"/>
+      <c r="K36" s="268"/>
+      <c r="L36" s="266" t="s">
         <v>239</v>
       </c>
-      <c r="H36" s="194"/>
-      <c r="I36" s="194"/>
-      <c r="J36" s="194"/>
-      <c r="K36" s="195"/>
-      <c r="L36" s="193" t="s">
+      <c r="M36" s="267"/>
+      <c r="N36" s="267"/>
+      <c r="O36" s="267"/>
+      <c r="P36" s="267"/>
+      <c r="Q36" s="267"/>
+      <c r="R36" s="267"/>
+      <c r="S36" s="268"/>
+      <c r="T36" s="238"/>
+      <c r="U36" s="243"/>
+      <c r="V36" s="206"/>
+    </row>
+    <row r="37" spans="1:25" ht="40" customHeight="1">
+      <c r="A37" s="269">
+        <v>15</v>
+      </c>
+      <c r="B37" s="270"/>
+      <c r="C37" s="188" t="s">
         <v>240</v>
       </c>
-      <c r="M36" s="194"/>
-      <c r="N36" s="194"/>
-      <c r="O36" s="194"/>
-      <c r="P36" s="194"/>
-      <c r="Q36" s="194"/>
-      <c r="R36" s="194"/>
-      <c r="S36" s="195"/>
-      <c r="T36" s="243"/>
-      <c r="U36" s="248"/>
-      <c r="V36" s="289"/>
-    </row>
-    <row r="37" spans="1:25" ht="40" customHeight="1">
-      <c r="A37" s="205">
-        <v>15</v>
-      </c>
-      <c r="B37" s="206"/>
-      <c r="C37" s="186" t="s">
-        <v>241</v>
-      </c>
-      <c r="D37" s="187"/>
-      <c r="E37" s="187"/>
-      <c r="F37" s="188"/>
-      <c r="G37" s="207" t="s">
+      <c r="D37" s="189"/>
+      <c r="E37" s="189"/>
+      <c r="F37" s="190"/>
+      <c r="G37" s="271" t="s">
+        <v>287</v>
+      </c>
+      <c r="H37" s="272"/>
+      <c r="I37" s="272"/>
+      <c r="J37" s="272"/>
+      <c r="K37" s="273"/>
+      <c r="L37" s="274" t="s">
         <v>288</v>
       </c>
-      <c r="H37" s="208"/>
-      <c r="I37" s="208"/>
-      <c r="J37" s="208"/>
-      <c r="K37" s="209"/>
-      <c r="L37" s="210" t="s">
+      <c r="M37" s="275"/>
+      <c r="N37" s="275"/>
+      <c r="O37" s="275"/>
+      <c r="P37" s="275"/>
+      <c r="Q37" s="275"/>
+      <c r="R37" s="275"/>
+      <c r="S37" s="276"/>
+      <c r="T37" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="M37" s="211"/>
-      <c r="N37" s="211"/>
-      <c r="O37" s="211"/>
-      <c r="P37" s="211"/>
-      <c r="Q37" s="211"/>
-      <c r="R37" s="211"/>
-      <c r="S37" s="212"/>
-      <c r="T37" s="21" t="s">
+      <c r="U37" s="244"/>
+      <c r="V37" s="207"/>
+    </row>
+    <row r="38" spans="1:25" ht="40" customHeight="1">
+      <c r="A38" s="256">
+        <v>16</v>
+      </c>
+      <c r="B38" s="262"/>
+      <c r="C38" s="188"/>
+      <c r="D38" s="189"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="190"/>
+      <c r="G38" s="277" t="s">
         <v>290</v>
       </c>
-      <c r="U37" s="249"/>
-      <c r="V37" s="290"/>
-    </row>
-    <row r="38" spans="1:25" ht="40" customHeight="1">
-      <c r="A38" s="171">
-        <v>16</v>
-      </c>
-      <c r="B38" s="173"/>
-      <c r="C38" s="186"/>
-      <c r="D38" s="187"/>
-      <c r="E38" s="187"/>
-      <c r="F38" s="188"/>
-      <c r="G38" s="256" t="s">
+      <c r="H38" s="278"/>
+      <c r="I38" s="278"/>
+      <c r="J38" s="278"/>
+      <c r="K38" s="279"/>
+      <c r="L38" s="246" t="s">
         <v>291</v>
       </c>
-      <c r="H38" s="257"/>
-      <c r="I38" s="257"/>
-      <c r="J38" s="257"/>
-      <c r="K38" s="258"/>
-      <c r="L38" s="259" t="s">
+      <c r="M38" s="247"/>
+      <c r="N38" s="247"/>
+      <c r="O38" s="247"/>
+      <c r="P38" s="247"/>
+      <c r="Q38" s="247"/>
+      <c r="R38" s="247"/>
+      <c r="S38" s="248"/>
+      <c r="T38" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="U38" s="241"/>
+      <c r="V38" s="207"/>
+    </row>
+    <row r="39" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A39" s="213"/>
+      <c r="B39" s="213"/>
+      <c r="C39" s="188"/>
+      <c r="D39" s="189"/>
+      <c r="E39" s="189"/>
+      <c r="F39" s="190"/>
+      <c r="G39" s="249" t="s">
         <v>292</v>
       </c>
-      <c r="M38" s="260"/>
-      <c r="N38" s="260"/>
-      <c r="O38" s="260"/>
-      <c r="P38" s="260"/>
-      <c r="Q38" s="260"/>
-      <c r="R38" s="260"/>
-      <c r="S38" s="261"/>
-      <c r="T38" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="U38" s="246"/>
-      <c r="V38" s="290"/>
-    </row>
-    <row r="39" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A39" s="296"/>
-      <c r="B39" s="296"/>
-      <c r="C39" s="186"/>
-      <c r="D39" s="187"/>
-      <c r="E39" s="187"/>
-      <c r="F39" s="188"/>
-      <c r="G39" s="217" t="s">
+      <c r="H39" s="250"/>
+      <c r="I39" s="250"/>
+      <c r="J39" s="250"/>
+      <c r="K39" s="250"/>
+      <c r="L39" s="250"/>
+      <c r="M39" s="250"/>
+      <c r="N39" s="250"/>
+      <c r="O39" s="250"/>
+      <c r="P39" s="250"/>
+      <c r="Q39" s="250"/>
+      <c r="R39" s="250"/>
+      <c r="S39" s="250"/>
+      <c r="T39" s="250"/>
+      <c r="U39" s="251"/>
+      <c r="V39" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="H39" s="218"/>
-      <c r="I39" s="218"/>
-      <c r="J39" s="218"/>
-      <c r="K39" s="218"/>
-      <c r="L39" s="218"/>
-      <c r="M39" s="218"/>
-      <c r="N39" s="218"/>
-      <c r="O39" s="218"/>
-      <c r="P39" s="218"/>
-      <c r="Q39" s="218"/>
-      <c r="R39" s="218"/>
-      <c r="S39" s="218"/>
-      <c r="T39" s="218"/>
-      <c r="U39" s="219"/>
-      <c r="V39" s="22" t="s">
-        <v>294</v>
-      </c>
     </row>
     <row r="40" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A40" s="296"/>
-      <c r="B40" s="296"/>
-      <c r="C40" s="186"/>
-      <c r="D40" s="187"/>
-      <c r="E40" s="187"/>
-      <c r="F40" s="188"/>
-      <c r="G40" s="262"/>
-      <c r="H40" s="263"/>
-      <c r="I40" s="263"/>
-      <c r="J40" s="263"/>
-      <c r="K40" s="263"/>
-      <c r="L40" s="263"/>
-      <c r="M40" s="263"/>
-      <c r="N40" s="263"/>
-      <c r="O40" s="263"/>
-      <c r="P40" s="263"/>
-      <c r="Q40" s="263"/>
-      <c r="R40" s="263"/>
-      <c r="S40" s="263"/>
-      <c r="T40" s="263"/>
-      <c r="U40" s="264"/>
-      <c r="V40" s="291"/>
+      <c r="A40" s="213"/>
+      <c r="B40" s="213"/>
+      <c r="C40" s="188"/>
+      <c r="D40" s="189"/>
+      <c r="E40" s="189"/>
+      <c r="F40" s="190"/>
+      <c r="G40" s="215"/>
+      <c r="H40" s="216"/>
+      <c r="I40" s="216"/>
+      <c r="J40" s="216"/>
+      <c r="K40" s="216"/>
+      <c r="L40" s="216"/>
+      <c r="M40" s="216"/>
+      <c r="N40" s="216"/>
+      <c r="O40" s="216"/>
+      <c r="P40" s="216"/>
+      <c r="Q40" s="216"/>
+      <c r="R40" s="216"/>
+      <c r="S40" s="216"/>
+      <c r="T40" s="216"/>
+      <c r="U40" s="217"/>
+      <c r="V40" s="208"/>
       <c r="W40" s="23"/>
     </row>
     <row r="41" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A41" s="296"/>
-      <c r="B41" s="296"/>
-      <c r="C41" s="186"/>
-      <c r="D41" s="187"/>
-      <c r="E41" s="187"/>
-      <c r="F41" s="188"/>
-      <c r="G41" s="265"/>
-      <c r="H41" s="266"/>
-      <c r="I41" s="266"/>
-      <c r="J41" s="266"/>
-      <c r="K41" s="266"/>
-      <c r="L41" s="266"/>
-      <c r="M41" s="266"/>
-      <c r="N41" s="266"/>
-      <c r="O41" s="266"/>
-      <c r="P41" s="266"/>
-      <c r="Q41" s="266"/>
-      <c r="R41" s="266"/>
-      <c r="S41" s="266"/>
-      <c r="T41" s="266"/>
-      <c r="U41" s="267"/>
-      <c r="V41" s="292"/>
+      <c r="A41" s="213"/>
+      <c r="B41" s="213"/>
+      <c r="C41" s="188"/>
+      <c r="D41" s="189"/>
+      <c r="E41" s="189"/>
+      <c r="F41" s="190"/>
+      <c r="G41" s="218"/>
+      <c r="H41" s="219"/>
+      <c r="I41" s="219"/>
+      <c r="J41" s="219"/>
+      <c r="K41" s="219"/>
+      <c r="L41" s="219"/>
+      <c r="M41" s="219"/>
+      <c r="N41" s="219"/>
+      <c r="O41" s="219"/>
+      <c r="P41" s="219"/>
+      <c r="Q41" s="219"/>
+      <c r="R41" s="219"/>
+      <c r="S41" s="219"/>
+      <c r="T41" s="219"/>
+      <c r="U41" s="220"/>
+      <c r="V41" s="209"/>
       <c r="W41" s="23"/>
     </row>
     <row r="42" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A42" s="296"/>
-      <c r="B42" s="296"/>
-      <c r="C42" s="186"/>
-      <c r="D42" s="187"/>
-      <c r="E42" s="187"/>
-      <c r="F42" s="188"/>
-      <c r="G42" s="265"/>
-      <c r="H42" s="266"/>
-      <c r="I42" s="266"/>
-      <c r="J42" s="266"/>
-      <c r="K42" s="266"/>
-      <c r="L42" s="266"/>
-      <c r="M42" s="266"/>
-      <c r="N42" s="266"/>
-      <c r="O42" s="266"/>
-      <c r="P42" s="266"/>
-      <c r="Q42" s="266"/>
-      <c r="R42" s="266"/>
-      <c r="S42" s="266"/>
-      <c r="T42" s="266"/>
-      <c r="U42" s="267"/>
-      <c r="V42" s="292"/>
+      <c r="A42" s="213"/>
+      <c r="B42" s="213"/>
+      <c r="C42" s="188"/>
+      <c r="D42" s="189"/>
+      <c r="E42" s="189"/>
+      <c r="F42" s="190"/>
+      <c r="G42" s="218"/>
+      <c r="H42" s="219"/>
+      <c r="I42" s="219"/>
+      <c r="J42" s="219"/>
+      <c r="K42" s="219"/>
+      <c r="L42" s="219"/>
+      <c r="M42" s="219"/>
+      <c r="N42" s="219"/>
+      <c r="O42" s="219"/>
+      <c r="P42" s="219"/>
+      <c r="Q42" s="219"/>
+      <c r="R42" s="219"/>
+      <c r="S42" s="219"/>
+      <c r="T42" s="219"/>
+      <c r="U42" s="220"/>
+      <c r="V42" s="209"/>
       <c r="W42" s="23"/>
       <c r="Y42" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A43" s="296"/>
-      <c r="B43" s="296"/>
-      <c r="C43" s="186"/>
-      <c r="D43" s="187"/>
-      <c r="E43" s="187"/>
-      <c r="F43" s="188"/>
-      <c r="G43" s="265"/>
-      <c r="H43" s="266"/>
-      <c r="I43" s="266"/>
-      <c r="J43" s="266"/>
-      <c r="K43" s="266"/>
-      <c r="L43" s="266"/>
-      <c r="M43" s="266"/>
-      <c r="N43" s="266"/>
-      <c r="O43" s="266"/>
-      <c r="P43" s="266"/>
-      <c r="Q43" s="266"/>
-      <c r="R43" s="266"/>
-      <c r="S43" s="266"/>
-      <c r="T43" s="266"/>
-      <c r="U43" s="267"/>
-      <c r="V43" s="292"/>
+      <c r="A43" s="213"/>
+      <c r="B43" s="213"/>
+      <c r="C43" s="188"/>
+      <c r="D43" s="189"/>
+      <c r="E43" s="189"/>
+      <c r="F43" s="190"/>
+      <c r="G43" s="218"/>
+      <c r="H43" s="219"/>
+      <c r="I43" s="219"/>
+      <c r="J43" s="219"/>
+      <c r="K43" s="219"/>
+      <c r="L43" s="219"/>
+      <c r="M43" s="219"/>
+      <c r="N43" s="219"/>
+      <c r="O43" s="219"/>
+      <c r="P43" s="219"/>
+      <c r="Q43" s="219"/>
+      <c r="R43" s="219"/>
+      <c r="S43" s="219"/>
+      <c r="T43" s="219"/>
+      <c r="U43" s="220"/>
+      <c r="V43" s="209"/>
       <c r="W43" s="23"/>
     </row>
     <row r="44" spans="1:25" s="1" customFormat="1" ht="260" customHeight="1">
-      <c r="A44" s="297"/>
-      <c r="B44" s="297"/>
-      <c r="C44" s="186"/>
-      <c r="D44" s="187"/>
-      <c r="E44" s="187"/>
-      <c r="F44" s="188"/>
-      <c r="G44" s="265"/>
-      <c r="H44" s="266"/>
-      <c r="I44" s="266"/>
-      <c r="J44" s="266"/>
-      <c r="K44" s="266"/>
-      <c r="L44" s="266"/>
-      <c r="M44" s="266"/>
-      <c r="N44" s="266"/>
-      <c r="O44" s="266"/>
-      <c r="P44" s="266"/>
-      <c r="Q44" s="266"/>
-      <c r="R44" s="266"/>
-      <c r="S44" s="266"/>
-      <c r="T44" s="266"/>
-      <c r="U44" s="267"/>
-      <c r="V44" s="292"/>
+      <c r="A44" s="214"/>
+      <c r="B44" s="214"/>
+      <c r="C44" s="188"/>
+      <c r="D44" s="189"/>
+      <c r="E44" s="189"/>
+      <c r="F44" s="190"/>
+      <c r="G44" s="218"/>
+      <c r="H44" s="219"/>
+      <c r="I44" s="219"/>
+      <c r="J44" s="219"/>
+      <c r="K44" s="219"/>
+      <c r="L44" s="219"/>
+      <c r="M44" s="219"/>
+      <c r="N44" s="219"/>
+      <c r="O44" s="219"/>
+      <c r="P44" s="219"/>
+      <c r="Q44" s="219"/>
+      <c r="R44" s="219"/>
+      <c r="S44" s="219"/>
+      <c r="T44" s="219"/>
+      <c r="U44" s="220"/>
+      <c r="V44" s="209"/>
       <c r="W44" s="23"/>
     </row>
     <row r="45" spans="1:25" ht="15">
       <c r="A45" s="14"/>
-      <c r="B45" s="220"/>
-      <c r="C45" s="220"/>
+      <c r="B45" s="228"/>
+      <c r="C45" s="228"/>
       <c r="D45" s="15"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
       <c r="G45" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="18"/>
-      <c r="J45" s="216" t="s">
-        <v>259</v>
+      <c r="J45" s="255" t="s">
+        <v>258</v>
       </c>
       <c r="K45" s="17"/>
-      <c r="L45" s="220"/>
-      <c r="M45" s="220"/>
-      <c r="N45" s="225" t="s">
-        <v>295</v>
-      </c>
-      <c r="O45" s="225"/>
-      <c r="P45" s="225"/>
-      <c r="Q45" s="225"/>
-      <c r="R45" s="225"/>
-      <c r="S45" s="225"/>
-      <c r="T45" s="225"/>
-      <c r="U45" s="227" t="s">
-        <v>261</v>
-      </c>
-      <c r="V45" s="228"/>
+      <c r="L45" s="228"/>
+      <c r="M45" s="228"/>
+      <c r="N45" s="196" t="s">
+        <v>294</v>
+      </c>
+      <c r="O45" s="196"/>
+      <c r="P45" s="196"/>
+      <c r="Q45" s="196"/>
+      <c r="R45" s="196"/>
+      <c r="S45" s="196"/>
+      <c r="T45" s="196"/>
+      <c r="U45" s="197" t="s">
+        <v>260</v>
+      </c>
+      <c r="V45" s="198"/>
     </row>
     <row r="46" spans="1:25" ht="15">
       <c r="A46" s="19"/>
-      <c r="B46" s="185"/>
-      <c r="C46" s="185"/>
+      <c r="B46" s="229"/>
+      <c r="C46" s="229"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="7"/>
       <c r="G46" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="8"/>
-      <c r="J46" s="190"/>
+      <c r="J46" s="252"/>
       <c r="K46" s="7"/>
-      <c r="L46" s="185"/>
-      <c r="M46" s="185"/>
-      <c r="N46" s="226"/>
-      <c r="O46" s="226"/>
-      <c r="P46" s="226"/>
-      <c r="Q46" s="226"/>
-      <c r="R46" s="226"/>
-      <c r="S46" s="226"/>
-      <c r="T46" s="226"/>
-      <c r="U46" s="229"/>
-      <c r="V46" s="230"/>
+      <c r="L46" s="229"/>
+      <c r="M46" s="229"/>
+      <c r="N46" s="186"/>
+      <c r="O46" s="186"/>
+      <c r="P46" s="186"/>
+      <c r="Q46" s="186"/>
+      <c r="R46" s="186"/>
+      <c r="S46" s="186"/>
+      <c r="T46" s="186"/>
+      <c r="U46" s="199"/>
+      <c r="V46" s="200"/>
     </row>
     <row r="47" spans="1:25" ht="15">
       <c r="A47" s="19"/>
-      <c r="B47" s="185"/>
-      <c r="C47" s="185"/>
+      <c r="B47" s="229"/>
+      <c r="C47" s="229"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="7"/>
       <c r="G47" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="190"/>
+      <c r="J47" s="252"/>
       <c r="K47" s="7"/>
-      <c r="L47" s="185"/>
-      <c r="M47" s="185"/>
-      <c r="N47" s="226"/>
-      <c r="O47" s="226"/>
-      <c r="P47" s="226"/>
-      <c r="Q47" s="226"/>
-      <c r="R47" s="226"/>
-      <c r="S47" s="226"/>
-      <c r="T47" s="226"/>
-      <c r="U47" s="231"/>
-      <c r="V47" s="232"/>
+      <c r="L47" s="229"/>
+      <c r="M47" s="229"/>
+      <c r="N47" s="186"/>
+      <c r="O47" s="186"/>
+      <c r="P47" s="186"/>
+      <c r="Q47" s="186"/>
+      <c r="R47" s="186"/>
+      <c r="S47" s="186"/>
+      <c r="T47" s="186"/>
+      <c r="U47" s="201"/>
+      <c r="V47" s="202"/>
     </row>
     <row r="48" spans="1:25" ht="15">
       <c r="A48" s="19"/>
-      <c r="B48" s="185"/>
-      <c r="C48" s="185"/>
+      <c r="B48" s="229"/>
+      <c r="C48" s="229"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="7"/>
       <c r="G48" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="8"/>
-      <c r="J48" s="190"/>
+      <c r="J48" s="252"/>
       <c r="K48" s="9"/>
-      <c r="L48" s="190"/>
-      <c r="M48" s="190"/>
-      <c r="N48" s="226" t="s">
+      <c r="L48" s="252"/>
+      <c r="M48" s="252"/>
+      <c r="N48" s="186" t="s">
+        <v>264</v>
+      </c>
+      <c r="O48" s="186"/>
+      <c r="P48" s="186"/>
+      <c r="Q48" s="186"/>
+      <c r="R48" s="186"/>
+      <c r="S48" s="186"/>
+      <c r="T48" s="186"/>
+      <c r="U48" s="182" t="s">
         <v>265</v>
       </c>
-      <c r="O48" s="226"/>
-      <c r="P48" s="226"/>
-      <c r="Q48" s="226"/>
-      <c r="R48" s="226"/>
-      <c r="S48" s="226"/>
-      <c r="T48" s="226"/>
-      <c r="U48" s="251" t="s">
-        <v>266</v>
-      </c>
-      <c r="V48" s="252"/>
+      <c r="V48" s="183"/>
     </row>
     <row r="49" spans="1:25" ht="15">
       <c r="A49" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="B49" s="253" t="s">
         <v>267</v>
       </c>
-      <c r="B49" s="191" t="s">
+      <c r="C49" s="253"/>
+      <c r="D49" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C49" s="191"/>
-      <c r="D49" s="10" t="s">
+      <c r="E49" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="F49" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="G49" s="254" t="s">
         <v>271</v>
       </c>
-      <c r="G49" s="192" t="s">
-        <v>272</v>
-      </c>
-      <c r="H49" s="192"/>
-      <c r="I49" s="192"/>
-      <c r="J49" s="192"/>
-      <c r="K49" s="191"/>
-      <c r="L49" s="191"/>
-      <c r="M49" s="191"/>
-      <c r="N49" s="250"/>
-      <c r="O49" s="250"/>
-      <c r="P49" s="250"/>
-      <c r="Q49" s="250"/>
-      <c r="R49" s="250"/>
-      <c r="S49" s="250"/>
-      <c r="T49" s="250"/>
-      <c r="U49" s="253"/>
-      <c r="V49" s="254"/>
+      <c r="H49" s="254"/>
+      <c r="I49" s="254"/>
+      <c r="J49" s="254"/>
+      <c r="K49" s="253"/>
+      <c r="L49" s="253"/>
+      <c r="M49" s="253"/>
+      <c r="N49" s="187"/>
+      <c r="O49" s="187"/>
+      <c r="P49" s="187"/>
+      <c r="Q49" s="187"/>
+      <c r="R49" s="187"/>
+      <c r="S49" s="187"/>
+      <c r="T49" s="187"/>
+      <c r="U49" s="184"/>
+      <c r="V49" s="185"/>
     </row>
     <row r="50" spans="1:25" ht="40" customHeight="1">
-      <c r="A50" s="238" t="s">
+      <c r="A50" s="172" t="s">
+        <v>232</v>
+      </c>
+      <c r="B50" s="173"/>
+      <c r="C50" s="176" t="s">
         <v>233</v>
       </c>
-      <c r="B50" s="221"/>
-      <c r="C50" s="271" t="s">
+      <c r="D50" s="177"/>
+      <c r="E50" s="177"/>
+      <c r="F50" s="178"/>
+      <c r="G50" s="263" t="s">
         <v>234</v>
       </c>
-      <c r="D50" s="272"/>
-      <c r="E50" s="272"/>
-      <c r="F50" s="273"/>
-      <c r="G50" s="163" t="s">
+      <c r="H50" s="264"/>
+      <c r="I50" s="264"/>
+      <c r="J50" s="264"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="264"/>
+      <c r="P50" s="264"/>
+      <c r="Q50" s="264"/>
+      <c r="R50" s="264"/>
+      <c r="S50" s="265"/>
+      <c r="T50" s="236" t="s">
         <v>235</v>
       </c>
-      <c r="H50" s="164"/>
-      <c r="I50" s="164"/>
-      <c r="J50" s="164"/>
-      <c r="K50" s="164"/>
-      <c r="L50" s="164"/>
-      <c r="M50" s="164"/>
-      <c r="N50" s="164"/>
-      <c r="O50" s="164"/>
-      <c r="P50" s="164"/>
-      <c r="Q50" s="164"/>
-      <c r="R50" s="164"/>
-      <c r="S50" s="165"/>
-      <c r="T50" s="241" t="s">
+      <c r="U50" s="239" t="s">
         <v>236</v>
       </c>
-      <c r="U50" s="244" t="s">
+      <c r="V50" s="203" t="s">
         <v>237</v>
       </c>
-      <c r="V50" s="287" t="s">
+    </row>
+    <row r="51" spans="1:25" ht="40" customHeight="1">
+      <c r="A51" s="191"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="193"/>
+      <c r="D51" s="194"/>
+      <c r="E51" s="194"/>
+      <c r="F51" s="195"/>
+      <c r="G51" s="266" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="51" spans="1:25" ht="40" customHeight="1">
-      <c r="A51" s="269"/>
-      <c r="B51" s="270"/>
-      <c r="C51" s="274"/>
-      <c r="D51" s="275"/>
-      <c r="E51" s="275"/>
-      <c r="F51" s="276"/>
-      <c r="G51" s="193" t="s">
+      <c r="H51" s="267"/>
+      <c r="I51" s="267"/>
+      <c r="J51" s="267"/>
+      <c r="K51" s="268"/>
+      <c r="L51" s="266" t="s">
         <v>239</v>
       </c>
-      <c r="H51" s="194"/>
-      <c r="I51" s="194"/>
-      <c r="J51" s="194"/>
-      <c r="K51" s="195"/>
-      <c r="L51" s="193" t="s">
+      <c r="M51" s="267"/>
+      <c r="N51" s="267"/>
+      <c r="O51" s="267"/>
+      <c r="P51" s="267"/>
+      <c r="Q51" s="267"/>
+      <c r="R51" s="267"/>
+      <c r="S51" s="268"/>
+      <c r="T51" s="238"/>
+      <c r="U51" s="243"/>
+      <c r="V51" s="206"/>
+    </row>
+    <row r="52" spans="1:25" ht="40" customHeight="1">
+      <c r="A52" s="269">
+        <v>17</v>
+      </c>
+      <c r="B52" s="270"/>
+      <c r="C52" s="188" t="s">
         <v>240</v>
       </c>
-      <c r="M51" s="194"/>
-      <c r="N51" s="194"/>
-      <c r="O51" s="194"/>
-      <c r="P51" s="194"/>
-      <c r="Q51" s="194"/>
-      <c r="R51" s="194"/>
-      <c r="S51" s="195"/>
-      <c r="T51" s="243"/>
-      <c r="U51" s="248"/>
-      <c r="V51" s="289"/>
-    </row>
-    <row r="52" spans="1:25" ht="40" customHeight="1">
-      <c r="A52" s="205">
-        <v>17</v>
-      </c>
-      <c r="B52" s="206"/>
-      <c r="C52" s="186" t="s">
-        <v>241</v>
-      </c>
-      <c r="D52" s="187"/>
-      <c r="E52" s="187"/>
-      <c r="F52" s="188"/>
-      <c r="G52" s="214" t="s">
+      <c r="D52" s="189"/>
+      <c r="E52" s="189"/>
+      <c r="F52" s="190"/>
+      <c r="G52" s="258" t="s">
+        <v>295</v>
+      </c>
+      <c r="H52" s="258"/>
+      <c r="I52" s="258"/>
+      <c r="J52" s="258"/>
+      <c r="K52" s="258"/>
+      <c r="L52" s="259" t="s">
         <v>296</v>
       </c>
-      <c r="H52" s="214"/>
-      <c r="I52" s="214"/>
-      <c r="J52" s="214"/>
-      <c r="K52" s="214"/>
-      <c r="L52" s="213" t="s">
+      <c r="M52" s="259"/>
+      <c r="N52" s="259"/>
+      <c r="O52" s="259"/>
+      <c r="P52" s="259"/>
+      <c r="Q52" s="259"/>
+      <c r="R52" s="259"/>
+      <c r="S52" s="259"/>
+      <c r="T52" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="U52" s="173"/>
+      <c r="V52" s="210"/>
+    </row>
+    <row r="53" spans="1:25" ht="40" customHeight="1">
+      <c r="A53" s="256">
+        <v>18</v>
+      </c>
+      <c r="B53" s="262"/>
+      <c r="C53" s="188"/>
+      <c r="D53" s="189"/>
+      <c r="E53" s="189"/>
+      <c r="F53" s="190"/>
+      <c r="G53" s="258" t="s">
         <v>297</v>
       </c>
-      <c r="M52" s="213"/>
-      <c r="N52" s="213"/>
-      <c r="O52" s="213"/>
-      <c r="P52" s="213"/>
-      <c r="Q52" s="213"/>
-      <c r="R52" s="213"/>
-      <c r="S52" s="213"/>
-      <c r="T52" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="U52" s="221"/>
-      <c r="V52" s="293"/>
-    </row>
-    <row r="53" spans="1:25" ht="40" customHeight="1">
-      <c r="A53" s="171">
-        <v>18</v>
-      </c>
-      <c r="B53" s="173"/>
-      <c r="C53" s="186"/>
-      <c r="D53" s="187"/>
-      <c r="E53" s="187"/>
-      <c r="F53" s="188"/>
-      <c r="G53" s="214" t="s">
+      <c r="H53" s="258"/>
+      <c r="I53" s="258"/>
+      <c r="J53" s="258"/>
+      <c r="K53" s="258"/>
+      <c r="L53" s="259" t="s">
+        <v>296</v>
+      </c>
+      <c r="M53" s="259"/>
+      <c r="N53" s="259"/>
+      <c r="O53" s="259"/>
+      <c r="P53" s="259"/>
+      <c r="Q53" s="259"/>
+      <c r="R53" s="259"/>
+      <c r="S53" s="259"/>
+      <c r="T53" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="U53" s="175"/>
+      <c r="V53" s="207"/>
+    </row>
+    <row r="54" spans="1:25" ht="40" customHeight="1">
+      <c r="A54" s="256">
+        <v>19</v>
+      </c>
+      <c r="B54" s="262"/>
+      <c r="C54" s="188"/>
+      <c r="D54" s="189"/>
+      <c r="E54" s="189"/>
+      <c r="F54" s="190"/>
+      <c r="G54" s="258" t="s">
         <v>298</v>
       </c>
-      <c r="H53" s="214"/>
-      <c r="I53" s="214"/>
-      <c r="J53" s="214"/>
-      <c r="K53" s="214"/>
-      <c r="L53" s="213" t="s">
-        <v>297</v>
-      </c>
-      <c r="M53" s="213"/>
-      <c r="N53" s="213"/>
-      <c r="O53" s="213"/>
-      <c r="P53" s="213"/>
-      <c r="Q53" s="213"/>
-      <c r="R53" s="213"/>
-      <c r="S53" s="213"/>
-      <c r="T53" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="U53" s="222"/>
-      <c r="V53" s="290"/>
-    </row>
-    <row r="54" spans="1:25" ht="40" customHeight="1">
-      <c r="A54" s="171">
-        <v>19</v>
-      </c>
-      <c r="B54" s="173"/>
-      <c r="C54" s="186"/>
-      <c r="D54" s="187"/>
-      <c r="E54" s="187"/>
-      <c r="F54" s="188"/>
-      <c r="G54" s="214" t="s">
+      <c r="H54" s="258"/>
+      <c r="I54" s="258"/>
+      <c r="J54" s="258"/>
+      <c r="K54" s="258"/>
+      <c r="L54" s="259" t="s">
+        <v>296</v>
+      </c>
+      <c r="M54" s="259"/>
+      <c r="N54" s="259"/>
+      <c r="O54" s="259"/>
+      <c r="P54" s="259"/>
+      <c r="Q54" s="259"/>
+      <c r="R54" s="259"/>
+      <c r="S54" s="259"/>
+      <c r="T54" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="U54" s="175"/>
+      <c r="V54" s="207"/>
+    </row>
+    <row r="55" spans="1:25" ht="40" customHeight="1">
+      <c r="A55" s="256"/>
+      <c r="B55" s="257"/>
+      <c r="C55" s="188"/>
+      <c r="D55" s="189"/>
+      <c r="E55" s="189"/>
+      <c r="F55" s="190"/>
+      <c r="G55" s="258" t="s">
         <v>299</v>
       </c>
-      <c r="H54" s="214"/>
-      <c r="I54" s="214"/>
-      <c r="J54" s="214"/>
-      <c r="K54" s="214"/>
-      <c r="L54" s="213" t="s">
-        <v>297</v>
-      </c>
-      <c r="M54" s="213"/>
-      <c r="N54" s="213"/>
-      <c r="O54" s="213"/>
-      <c r="P54" s="213"/>
-      <c r="Q54" s="213"/>
-      <c r="R54" s="213"/>
-      <c r="S54" s="213"/>
-      <c r="T54" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="U54" s="222"/>
-      <c r="V54" s="290"/>
-    </row>
-    <row r="55" spans="1:25" ht="40" customHeight="1">
-      <c r="A55" s="171"/>
-      <c r="B55" s="215"/>
-      <c r="C55" s="186"/>
-      <c r="D55" s="187"/>
-      <c r="E55" s="187"/>
-      <c r="F55" s="188"/>
-      <c r="G55" s="214" t="s">
+      <c r="H55" s="258"/>
+      <c r="I55" s="258"/>
+      <c r="J55" s="258"/>
+      <c r="K55" s="258"/>
+      <c r="L55" s="259" t="s">
+        <v>296</v>
+      </c>
+      <c r="M55" s="259"/>
+      <c r="N55" s="259"/>
+      <c r="O55" s="259"/>
+      <c r="P55" s="259"/>
+      <c r="Q55" s="259"/>
+      <c r="R55" s="259"/>
+      <c r="S55" s="259"/>
+      <c r="T55" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="U55" s="260"/>
+      <c r="V55" s="211"/>
+    </row>
+    <row r="56" spans="1:25" ht="40" customHeight="1">
+      <c r="A56" s="256"/>
+      <c r="B56" s="257"/>
+      <c r="C56" s="188"/>
+      <c r="D56" s="189"/>
+      <c r="E56" s="189"/>
+      <c r="F56" s="190"/>
+      <c r="G56" s="258" t="s">
         <v>300</v>
       </c>
-      <c r="H55" s="214"/>
-      <c r="I55" s="214"/>
-      <c r="J55" s="214"/>
-      <c r="K55" s="214"/>
-      <c r="L55" s="213" t="s">
-        <v>297</v>
-      </c>
-      <c r="M55" s="213"/>
-      <c r="N55" s="213"/>
-      <c r="O55" s="213"/>
-      <c r="P55" s="213"/>
-      <c r="Q55" s="213"/>
-      <c r="R55" s="213"/>
-      <c r="S55" s="213"/>
-      <c r="T55" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="U55" s="223"/>
-      <c r="V55" s="294"/>
-    </row>
-    <row r="56" spans="1:25" ht="40" customHeight="1">
-      <c r="A56" s="171"/>
-      <c r="B56" s="215"/>
-      <c r="C56" s="186"/>
-      <c r="D56" s="187"/>
-      <c r="E56" s="187"/>
-      <c r="F56" s="188"/>
-      <c r="G56" s="214" t="s">
-        <v>301</v>
-      </c>
-      <c r="H56" s="214"/>
-      <c r="I56" s="214"/>
-      <c r="J56" s="214"/>
-      <c r="K56" s="214"/>
-      <c r="L56" s="213" t="s">
-        <v>297</v>
-      </c>
-      <c r="M56" s="213"/>
-      <c r="N56" s="213"/>
-      <c r="O56" s="213"/>
-      <c r="P56" s="213"/>
-      <c r="Q56" s="213"/>
-      <c r="R56" s="213"/>
-      <c r="S56" s="213"/>
+      <c r="H56" s="258"/>
+      <c r="I56" s="258"/>
+      <c r="J56" s="258"/>
+      <c r="K56" s="258"/>
+      <c r="L56" s="259" t="s">
+        <v>296</v>
+      </c>
+      <c r="M56" s="259"/>
+      <c r="N56" s="259"/>
+      <c r="O56" s="259"/>
+      <c r="P56" s="259"/>
+      <c r="Q56" s="259"/>
+      <c r="R56" s="259"/>
+      <c r="S56" s="259"/>
       <c r="T56" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="U56" s="224"/>
-      <c r="V56" s="295"/>
+        <v>289</v>
+      </c>
+      <c r="U56" s="261"/>
+      <c r="V56" s="212"/>
     </row>
     <row r="57" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A57" s="296"/>
-      <c r="B57" s="296"/>
-      <c r="C57" s="186"/>
-      <c r="D57" s="187"/>
-      <c r="E57" s="187"/>
-      <c r="F57" s="188"/>
-      <c r="G57" s="217" t="s">
+      <c r="A57" s="213"/>
+      <c r="B57" s="213"/>
+      <c r="C57" s="188"/>
+      <c r="D57" s="189"/>
+      <c r="E57" s="189"/>
+      <c r="F57" s="190"/>
+      <c r="G57" s="249" t="s">
+        <v>292</v>
+      </c>
+      <c r="H57" s="250"/>
+      <c r="I57" s="250"/>
+      <c r="J57" s="250"/>
+      <c r="K57" s="250"/>
+      <c r="L57" s="250"/>
+      <c r="M57" s="250"/>
+      <c r="N57" s="250"/>
+      <c r="O57" s="250"/>
+      <c r="P57" s="250"/>
+      <c r="Q57" s="250"/>
+      <c r="R57" s="250"/>
+      <c r="S57" s="250"/>
+      <c r="T57" s="250"/>
+      <c r="U57" s="251"/>
+      <c r="V57" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="H57" s="218"/>
-      <c r="I57" s="218"/>
-      <c r="J57" s="218"/>
-      <c r="K57" s="218"/>
-      <c r="L57" s="218"/>
-      <c r="M57" s="218"/>
-      <c r="N57" s="218"/>
-      <c r="O57" s="218"/>
-      <c r="P57" s="218"/>
-      <c r="Q57" s="218"/>
-      <c r="R57" s="218"/>
-      <c r="S57" s="218"/>
-      <c r="T57" s="218"/>
-      <c r="U57" s="219"/>
-      <c r="V57" s="22" t="s">
-        <v>294</v>
-      </c>
     </row>
     <row r="58" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A58" s="296"/>
-      <c r="B58" s="296"/>
-      <c r="C58" s="186"/>
-      <c r="D58" s="187"/>
-      <c r="E58" s="187"/>
-      <c r="F58" s="188"/>
-      <c r="G58" s="262"/>
-      <c r="H58" s="263"/>
-      <c r="I58" s="263"/>
-      <c r="J58" s="263"/>
-      <c r="K58" s="263"/>
-      <c r="L58" s="263"/>
-      <c r="M58" s="263"/>
-      <c r="N58" s="263"/>
-      <c r="O58" s="263"/>
-      <c r="P58" s="263"/>
-      <c r="Q58" s="263"/>
-      <c r="R58" s="263"/>
-      <c r="S58" s="263"/>
-      <c r="T58" s="263"/>
-      <c r="U58" s="264"/>
-      <c r="V58" s="291"/>
+      <c r="A58" s="213"/>
+      <c r="B58" s="213"/>
+      <c r="C58" s="188"/>
+      <c r="D58" s="189"/>
+      <c r="E58" s="189"/>
+      <c r="F58" s="190"/>
+      <c r="G58" s="215"/>
+      <c r="H58" s="216"/>
+      <c r="I58" s="216"/>
+      <c r="J58" s="216"/>
+      <c r="K58" s="216"/>
+      <c r="L58" s="216"/>
+      <c r="M58" s="216"/>
+      <c r="N58" s="216"/>
+      <c r="O58" s="216"/>
+      <c r="P58" s="216"/>
+      <c r="Q58" s="216"/>
+      <c r="R58" s="216"/>
+      <c r="S58" s="216"/>
+      <c r="T58" s="216"/>
+      <c r="U58" s="217"/>
+      <c r="V58" s="208"/>
       <c r="W58" s="23"/>
     </row>
     <row r="59" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A59" s="296"/>
-      <c r="B59" s="296"/>
-      <c r="C59" s="186"/>
-      <c r="D59" s="187"/>
-      <c r="E59" s="187"/>
-      <c r="F59" s="188"/>
-      <c r="G59" s="265"/>
-      <c r="H59" s="266"/>
-      <c r="I59" s="266"/>
-      <c r="J59" s="266"/>
-      <c r="K59" s="266"/>
-      <c r="L59" s="266"/>
-      <c r="M59" s="266"/>
-      <c r="N59" s="266"/>
-      <c r="O59" s="266"/>
-      <c r="P59" s="266"/>
-      <c r="Q59" s="266"/>
-      <c r="R59" s="266"/>
-      <c r="S59" s="266"/>
-      <c r="T59" s="266"/>
-      <c r="U59" s="267"/>
-      <c r="V59" s="292"/>
+      <c r="A59" s="213"/>
+      <c r="B59" s="213"/>
+      <c r="C59" s="188"/>
+      <c r="D59" s="189"/>
+      <c r="E59" s="189"/>
+      <c r="F59" s="190"/>
+      <c r="G59" s="218"/>
+      <c r="H59" s="219"/>
+      <c r="I59" s="219"/>
+      <c r="J59" s="219"/>
+      <c r="K59" s="219"/>
+      <c r="L59" s="219"/>
+      <c r="M59" s="219"/>
+      <c r="N59" s="219"/>
+      <c r="O59" s="219"/>
+      <c r="P59" s="219"/>
+      <c r="Q59" s="219"/>
+      <c r="R59" s="219"/>
+      <c r="S59" s="219"/>
+      <c r="T59" s="219"/>
+      <c r="U59" s="220"/>
+      <c r="V59" s="209"/>
       <c r="W59" s="23"/>
     </row>
     <row r="60" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A60" s="296"/>
-      <c r="B60" s="296"/>
-      <c r="C60" s="186"/>
-      <c r="D60" s="187"/>
-      <c r="E60" s="187"/>
-      <c r="F60" s="188"/>
-      <c r="G60" s="265"/>
-      <c r="H60" s="266"/>
-      <c r="I60" s="266"/>
-      <c r="J60" s="266"/>
-      <c r="K60" s="266"/>
-      <c r="L60" s="266"/>
-      <c r="M60" s="266"/>
-      <c r="N60" s="266"/>
-      <c r="O60" s="266"/>
-      <c r="P60" s="266"/>
-      <c r="Q60" s="266"/>
-      <c r="R60" s="266"/>
-      <c r="S60" s="266"/>
-      <c r="T60" s="266"/>
-      <c r="U60" s="267"/>
-      <c r="V60" s="292"/>
+      <c r="A60" s="213"/>
+      <c r="B60" s="213"/>
+      <c r="C60" s="188"/>
+      <c r="D60" s="189"/>
+      <c r="E60" s="189"/>
+      <c r="F60" s="190"/>
+      <c r="G60" s="218"/>
+      <c r="H60" s="219"/>
+      <c r="I60" s="219"/>
+      <c r="J60" s="219"/>
+      <c r="K60" s="219"/>
+      <c r="L60" s="219"/>
+      <c r="M60" s="219"/>
+      <c r="N60" s="219"/>
+      <c r="O60" s="219"/>
+      <c r="P60" s="219"/>
+      <c r="Q60" s="219"/>
+      <c r="R60" s="219"/>
+      <c r="S60" s="219"/>
+      <c r="T60" s="219"/>
+      <c r="U60" s="220"/>
+      <c r="V60" s="209"/>
       <c r="W60" s="23"/>
       <c r="Y60" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A61" s="296"/>
-      <c r="B61" s="296"/>
-      <c r="C61" s="186"/>
-      <c r="D61" s="187"/>
-      <c r="E61" s="187"/>
-      <c r="F61" s="188"/>
-      <c r="G61" s="265"/>
-      <c r="H61" s="266"/>
-      <c r="I61" s="266"/>
-      <c r="J61" s="266"/>
-      <c r="K61" s="266"/>
-      <c r="L61" s="266"/>
-      <c r="M61" s="266"/>
-      <c r="N61" s="266"/>
-      <c r="O61" s="266"/>
-      <c r="P61" s="266"/>
-      <c r="Q61" s="266"/>
-      <c r="R61" s="266"/>
-      <c r="S61" s="266"/>
-      <c r="T61" s="266"/>
-      <c r="U61" s="267"/>
-      <c r="V61" s="292"/>
+      <c r="A61" s="213"/>
+      <c r="B61" s="213"/>
+      <c r="C61" s="188"/>
+      <c r="D61" s="189"/>
+      <c r="E61" s="189"/>
+      <c r="F61" s="190"/>
+      <c r="G61" s="218"/>
+      <c r="H61" s="219"/>
+      <c r="I61" s="219"/>
+      <c r="J61" s="219"/>
+      <c r="K61" s="219"/>
+      <c r="L61" s="219"/>
+      <c r="M61" s="219"/>
+      <c r="N61" s="219"/>
+      <c r="O61" s="219"/>
+      <c r="P61" s="219"/>
+      <c r="Q61" s="219"/>
+      <c r="R61" s="219"/>
+      <c r="S61" s="219"/>
+      <c r="T61" s="219"/>
+      <c r="U61" s="220"/>
+      <c r="V61" s="209"/>
       <c r="W61" s="23"/>
     </row>
     <row r="62" spans="1:25" s="1" customFormat="1" ht="260" customHeight="1">
-      <c r="A62" s="297"/>
-      <c r="B62" s="297"/>
-      <c r="C62" s="186"/>
-      <c r="D62" s="187"/>
-      <c r="E62" s="187"/>
-      <c r="F62" s="188"/>
-      <c r="G62" s="265"/>
-      <c r="H62" s="266"/>
-      <c r="I62" s="266"/>
-      <c r="J62" s="266"/>
-      <c r="K62" s="266"/>
-      <c r="L62" s="266"/>
-      <c r="M62" s="266"/>
-      <c r="N62" s="266"/>
-      <c r="O62" s="266"/>
-      <c r="P62" s="266"/>
-      <c r="Q62" s="266"/>
-      <c r="R62" s="266"/>
-      <c r="S62" s="266"/>
-      <c r="T62" s="266"/>
-      <c r="U62" s="267"/>
-      <c r="V62" s="292"/>
+      <c r="A62" s="214"/>
+      <c r="B62" s="214"/>
+      <c r="C62" s="188"/>
+      <c r="D62" s="189"/>
+      <c r="E62" s="189"/>
+      <c r="F62" s="190"/>
+      <c r="G62" s="218"/>
+      <c r="H62" s="219"/>
+      <c r="I62" s="219"/>
+      <c r="J62" s="219"/>
+      <c r="K62" s="219"/>
+      <c r="L62" s="219"/>
+      <c r="M62" s="219"/>
+      <c r="N62" s="219"/>
+      <c r="O62" s="219"/>
+      <c r="P62" s="219"/>
+      <c r="Q62" s="219"/>
+      <c r="R62" s="219"/>
+      <c r="S62" s="219"/>
+      <c r="T62" s="219"/>
+      <c r="U62" s="220"/>
+      <c r="V62" s="209"/>
       <c r="W62" s="23"/>
     </row>
     <row r="63" spans="1:25" ht="15">
       <c r="A63" s="14"/>
-      <c r="B63" s="220"/>
-      <c r="C63" s="220"/>
+      <c r="B63" s="228"/>
+      <c r="C63" s="228"/>
       <c r="D63" s="15"/>
       <c r="E63" s="15"/>
       <c r="F63" s="15"/>
       <c r="G63" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H63" s="17"/>
       <c r="I63" s="18"/>
-      <c r="J63" s="216" t="s">
-        <v>259</v>
+      <c r="J63" s="255" t="s">
+        <v>258</v>
       </c>
       <c r="K63" s="17"/>
-      <c r="L63" s="220"/>
-      <c r="M63" s="220"/>
-      <c r="N63" s="225" t="s">
-        <v>302</v>
-      </c>
-      <c r="O63" s="225"/>
-      <c r="P63" s="225"/>
-      <c r="Q63" s="225"/>
-      <c r="R63" s="225"/>
-      <c r="S63" s="225"/>
-      <c r="T63" s="225"/>
-      <c r="U63" s="227" t="s">
-        <v>261</v>
-      </c>
-      <c r="V63" s="228"/>
+      <c r="L63" s="228"/>
+      <c r="M63" s="228"/>
+      <c r="N63" s="196" t="s">
+        <v>301</v>
+      </c>
+      <c r="O63" s="196"/>
+      <c r="P63" s="196"/>
+      <c r="Q63" s="196"/>
+      <c r="R63" s="196"/>
+      <c r="S63" s="196"/>
+      <c r="T63" s="196"/>
+      <c r="U63" s="197" t="s">
+        <v>260</v>
+      </c>
+      <c r="V63" s="198"/>
     </row>
     <row r="64" spans="1:25" ht="15">
       <c r="A64" s="19"/>
-      <c r="B64" s="185"/>
-      <c r="C64" s="185"/>
+      <c r="B64" s="229"/>
+      <c r="C64" s="229"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="7"/>
       <c r="G64" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="190"/>
+      <c r="J64" s="252"/>
       <c r="K64" s="7"/>
-      <c r="L64" s="185"/>
-      <c r="M64" s="185"/>
-      <c r="N64" s="226"/>
-      <c r="O64" s="226"/>
-      <c r="P64" s="226"/>
-      <c r="Q64" s="226"/>
-      <c r="R64" s="226"/>
-      <c r="S64" s="226"/>
-      <c r="T64" s="226"/>
-      <c r="U64" s="229"/>
-      <c r="V64" s="230"/>
+      <c r="L64" s="229"/>
+      <c r="M64" s="229"/>
+      <c r="N64" s="186"/>
+      <c r="O64" s="186"/>
+      <c r="P64" s="186"/>
+      <c r="Q64" s="186"/>
+      <c r="R64" s="186"/>
+      <c r="S64" s="186"/>
+      <c r="T64" s="186"/>
+      <c r="U64" s="199"/>
+      <c r="V64" s="200"/>
     </row>
     <row r="65" spans="1:22" ht="15">
       <c r="A65" s="19"/>
-      <c r="B65" s="185"/>
-      <c r="C65" s="185"/>
+      <c r="B65" s="229"/>
+      <c r="C65" s="229"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="7"/>
       <c r="G65" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H65" s="7"/>
       <c r="I65" s="8"/>
-      <c r="J65" s="190"/>
+      <c r="J65" s="252"/>
       <c r="K65" s="7"/>
-      <c r="L65" s="185"/>
-      <c r="M65" s="185"/>
-      <c r="N65" s="226"/>
-      <c r="O65" s="226"/>
-      <c r="P65" s="226"/>
-      <c r="Q65" s="226"/>
-      <c r="R65" s="226"/>
-      <c r="S65" s="226"/>
-      <c r="T65" s="226"/>
-      <c r="U65" s="231"/>
-      <c r="V65" s="232"/>
+      <c r="L65" s="229"/>
+      <c r="M65" s="229"/>
+      <c r="N65" s="186"/>
+      <c r="O65" s="186"/>
+      <c r="P65" s="186"/>
+      <c r="Q65" s="186"/>
+      <c r="R65" s="186"/>
+      <c r="S65" s="186"/>
+      <c r="T65" s="186"/>
+      <c r="U65" s="201"/>
+      <c r="V65" s="202"/>
     </row>
     <row r="66" spans="1:22" ht="15">
       <c r="A66" s="19"/>
-      <c r="B66" s="185"/>
-      <c r="C66" s="185"/>
+      <c r="B66" s="229"/>
+      <c r="C66" s="229"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="7"/>
       <c r="G66" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="190"/>
+      <c r="J66" s="252"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="190"/>
-      <c r="M66" s="190"/>
-      <c r="N66" s="226" t="s">
+      <c r="L66" s="252"/>
+      <c r="M66" s="252"/>
+      <c r="N66" s="186" t="s">
+        <v>264</v>
+      </c>
+      <c r="O66" s="186"/>
+      <c r="P66" s="186"/>
+      <c r="Q66" s="186"/>
+      <c r="R66" s="186"/>
+      <c r="S66" s="186"/>
+      <c r="T66" s="186"/>
+      <c r="U66" s="182" t="s">
         <v>265</v>
       </c>
-      <c r="O66" s="226"/>
-      <c r="P66" s="226"/>
-      <c r="Q66" s="226"/>
-      <c r="R66" s="226"/>
-      <c r="S66" s="226"/>
-      <c r="T66" s="226"/>
-      <c r="U66" s="251" t="s">
-        <v>266</v>
-      </c>
-      <c r="V66" s="252"/>
+      <c r="V66" s="183"/>
     </row>
     <row r="67" spans="1:22" ht="15">
       <c r="A67" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="B67" s="253" t="s">
         <v>267</v>
       </c>
-      <c r="B67" s="191" t="s">
+      <c r="C67" s="253"/>
+      <c r="D67" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C67" s="191"/>
-      <c r="D67" s="10" t="s">
+      <c r="E67" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="F67" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="G67" s="254" t="s">
         <v>271</v>
       </c>
-      <c r="G67" s="192" t="s">
-        <v>272</v>
-      </c>
-      <c r="H67" s="192"/>
-      <c r="I67" s="192"/>
-      <c r="J67" s="192"/>
-      <c r="K67" s="191"/>
-      <c r="L67" s="191"/>
-      <c r="M67" s="191"/>
-      <c r="N67" s="250"/>
-      <c r="O67" s="250"/>
-      <c r="P67" s="250"/>
-      <c r="Q67" s="250"/>
-      <c r="R67" s="250"/>
-      <c r="S67" s="250"/>
-      <c r="T67" s="250"/>
-      <c r="U67" s="253"/>
-      <c r="V67" s="254"/>
+      <c r="H67" s="254"/>
+      <c r="I67" s="254"/>
+      <c r="J67" s="254"/>
+      <c r="K67" s="253"/>
+      <c r="L67" s="253"/>
+      <c r="M67" s="253"/>
+      <c r="N67" s="187"/>
+      <c r="O67" s="187"/>
+      <c r="P67" s="187"/>
+      <c r="Q67" s="187"/>
+      <c r="R67" s="187"/>
+      <c r="S67" s="187"/>
+      <c r="T67" s="187"/>
+      <c r="U67" s="184"/>
+      <c r="V67" s="185"/>
     </row>
   </sheetData>
   <mergeCells count="180">
+    <mergeCell ref="G3:S3"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="L4:S4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="L5:S5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="L6:S6"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="L10:S10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="L11:S11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="C5:F11"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:S7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="L8:S8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="L9:S9"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="L22:S22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="L23:S23"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="G19:S19"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="L20:S20"/>
+    <mergeCell ref="A17:V18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:F20"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="G35:S35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="L36:S36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="L37:S37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="L53:S53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="G54:K54"/>
+    <mergeCell ref="L54:S54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="G55:K55"/>
+    <mergeCell ref="L55:S55"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="K49:M49"/>
+    <mergeCell ref="G50:S50"/>
+    <mergeCell ref="G51:K51"/>
+    <mergeCell ref="L51:S51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="L52:S52"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="J28:J31"/>
+    <mergeCell ref="J45:J48"/>
+    <mergeCell ref="J63:J66"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="G56:K56"/>
+    <mergeCell ref="L56:S56"/>
+    <mergeCell ref="G57:U57"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="U52:U56"/>
+    <mergeCell ref="N63:T65"/>
+    <mergeCell ref="U63:V65"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="G53:K53"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="T50:T51"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="U5:U11"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="U21:U27"/>
+    <mergeCell ref="U35:U36"/>
+    <mergeCell ref="U37:U38"/>
+    <mergeCell ref="U50:U51"/>
+    <mergeCell ref="N15:T16"/>
+    <mergeCell ref="U15:V16"/>
+    <mergeCell ref="N12:T14"/>
+    <mergeCell ref="U12:V14"/>
+    <mergeCell ref="L38:S38"/>
+    <mergeCell ref="G39:U39"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="G40:U44"/>
+    <mergeCell ref="A33:V34"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:F36"/>
+    <mergeCell ref="N31:T32"/>
+    <mergeCell ref="U31:V32"/>
+    <mergeCell ref="N28:T30"/>
+    <mergeCell ref="U28:V30"/>
+    <mergeCell ref="C21:F27"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="L27:S27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="L24:S24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="L25:S25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="L26:S26"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="L21:S21"/>
     <mergeCell ref="A1:V2"/>
     <mergeCell ref="A3:B4"/>
     <mergeCell ref="C3:F4"/>
@@ -13628,162 +13775,6 @@
     <mergeCell ref="G58:U62"/>
     <mergeCell ref="C37:F44"/>
     <mergeCell ref="A39:B44"/>
-    <mergeCell ref="N28:T30"/>
-    <mergeCell ref="U28:V30"/>
-    <mergeCell ref="C21:F27"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="G27:K27"/>
-    <mergeCell ref="L27:S27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G24:K24"/>
-    <mergeCell ref="L24:S24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="G25:K25"/>
-    <mergeCell ref="L25:S25"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="T35:T36"/>
-    <mergeCell ref="T50:T51"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="U5:U11"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="U21:U27"/>
-    <mergeCell ref="U35:U36"/>
-    <mergeCell ref="U37:U38"/>
-    <mergeCell ref="U50:U51"/>
-    <mergeCell ref="N15:T16"/>
-    <mergeCell ref="U15:V16"/>
-    <mergeCell ref="N12:T14"/>
-    <mergeCell ref="U12:V14"/>
-    <mergeCell ref="L38:S38"/>
-    <mergeCell ref="G39:U39"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="G40:U44"/>
-    <mergeCell ref="A33:V34"/>
-    <mergeCell ref="A35:B36"/>
-    <mergeCell ref="C35:F36"/>
-    <mergeCell ref="N31:T32"/>
-    <mergeCell ref="U31:V32"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="G67:J67"/>
-    <mergeCell ref="K67:M67"/>
-    <mergeCell ref="J12:J15"/>
-    <mergeCell ref="J28:J31"/>
-    <mergeCell ref="J45:J48"/>
-    <mergeCell ref="J63:J66"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="G56:K56"/>
-    <mergeCell ref="L56:S56"/>
-    <mergeCell ref="G57:U57"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="U52:U56"/>
-    <mergeCell ref="N63:T65"/>
-    <mergeCell ref="U63:V65"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="G53:K53"/>
-    <mergeCell ref="L53:S53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="G54:K54"/>
-    <mergeCell ref="L54:S54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="G55:K55"/>
-    <mergeCell ref="L55:S55"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="G49:J49"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="G50:S50"/>
-    <mergeCell ref="G51:K51"/>
-    <mergeCell ref="L51:S51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="G52:K52"/>
-    <mergeCell ref="L52:S52"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="G35:S35"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="L36:S36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="L37:S37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="G26:K26"/>
-    <mergeCell ref="L26:S26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="L21:S21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G22:K22"/>
-    <mergeCell ref="L22:S22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="G23:K23"/>
-    <mergeCell ref="L23:S23"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="G19:S19"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="L20:S20"/>
-    <mergeCell ref="A17:V18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:F20"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="L10:S10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="L11:S11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="C5:F11"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="L7:S7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="L8:S8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="L9:S9"/>
-    <mergeCell ref="G3:S3"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="L4:S4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="L5:S5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="L6:S6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="整车型号" prompt="与封皮“整车型号”一致" sqref="U12 U28 U45 U63" xr:uid="{00000000-0002-0000-0400-000000000000}"/>
